--- a/research/traditional_assets/database/data/jamaica/jamaica_retail_special_lines.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_retail_special_lines.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1468419914954759</v>
+        <v>0.1465086365167372</v>
       </c>
       <c r="C2">
-        <v>76.71598101056846</v>
+        <v>76.17889375704974</v>
       </c>
       <c r="D2">
-        <v>69.15598101056845</v>
+        <v>69.38489375704974</v>
       </c>
       <c r="E2">
-        <v>-10.6</v>
+        <v>-9.834</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.766</v>
       </c>
       <c r="G2">
         <v>7.56</v>
@@ -1451,28 +1451,28 @@
         <v>4.56</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0385298</v>
       </c>
       <c r="N2">
-        <v>4.56</v>
+        <v>4.5214702</v>
       </c>
       <c r="O2">
-        <v>1.14</v>
+        <v>1.13036755</v>
       </c>
       <c r="P2">
-        <v>3.42</v>
+        <v>3.39110265</v>
       </c>
       <c r="Q2">
-        <v>4.03</v>
+        <v>4.00110265</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1468419914954759</v>
+        <v>0.1476074611280173</v>
       </c>
       <c r="T2">
-        <v>0.9771532823765234</v>
+        <v>0.9845559587581637</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>118.3499525042954</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1465086365167372</v>
+        <v>0.1461752815379985</v>
       </c>
       <c r="C3">
-        <v>76.17889375704974</v>
+        <v>75.64332698153252</v>
       </c>
       <c r="D3">
-        <v>69.38489375704974</v>
+        <v>69.61532698153252</v>
       </c>
       <c r="E3">
-        <v>-9.834</v>
+        <v>-9.068</v>
       </c>
       <c r="F3">
-        <v>0.766</v>
+        <v>1.532</v>
       </c>
       <c r="G3">
         <v>7.56</v>
@@ -1533,28 +1533,28 @@
         <v>4.56</v>
       </c>
       <c r="M3">
-        <v>0.0385298</v>
+        <v>0.07705959999999999</v>
       </c>
       <c r="N3">
-        <v>4.5214702</v>
+        <v>4.482940399999999</v>
       </c>
       <c r="O3">
-        <v>1.13036755</v>
+        <v>1.1207351</v>
       </c>
       <c r="P3">
-        <v>3.39110265</v>
+        <v>3.362205299999999</v>
       </c>
       <c r="Q3">
-        <v>4.00110265</v>
+        <v>3.9722053</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1476074611280173</v>
+        <v>0.1483885525897944</v>
       </c>
       <c r="T3">
-        <v>0.9845559587581637</v>
+        <v>0.9921097101680009</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>118.3499525042954</v>
+        <v>59.17497625214769</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1461752815379985</v>
+        <v>0.1458419265592598</v>
       </c>
       <c r="C4">
-        <v>75.64332698153252</v>
+        <v>75.10929588341159</v>
       </c>
       <c r="D4">
-        <v>69.61532698153252</v>
+        <v>69.84729588341159</v>
       </c>
       <c r="E4">
-        <v>-9.068</v>
+        <v>-8.302</v>
       </c>
       <c r="F4">
-        <v>1.532</v>
+        <v>2.298</v>
       </c>
       <c r="G4">
         <v>7.56</v>
@@ -1615,28 +1615,28 @@
         <v>4.56</v>
       </c>
       <c r="M4">
-        <v>0.07705959999999999</v>
+        <v>0.1155894</v>
       </c>
       <c r="N4">
-        <v>4.482940399999999</v>
+        <v>4.444410599999999</v>
       </c>
       <c r="O4">
-        <v>1.1207351</v>
+        <v>1.11110265</v>
       </c>
       <c r="P4">
-        <v>3.362205299999999</v>
+        <v>3.33330795</v>
       </c>
       <c r="Q4">
-        <v>3.9722053</v>
+        <v>3.94330795</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1483885525897944</v>
+        <v>0.1491857490301647</v>
       </c>
       <c r="T4">
-        <v>0.9921097101680009</v>
+        <v>0.9998192090295871</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>59.17497625214769</v>
+        <v>39.44998416809847</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1458419265592598</v>
+        <v>0.1455085715805211</v>
       </c>
       <c r="C5">
-        <v>75.10929588341159</v>
+        <v>74.57681586534576</v>
       </c>
       <c r="D5">
-        <v>69.84729588341159</v>
+        <v>70.08081586534577</v>
       </c>
       <c r="E5">
-        <v>-8.302</v>
+        <v>-7.536</v>
       </c>
       <c r="F5">
-        <v>2.298</v>
+        <v>3.064</v>
       </c>
       <c r="G5">
         <v>7.56</v>
@@ -1697,28 +1697,28 @@
         <v>4.56</v>
       </c>
       <c r="M5">
-        <v>0.1155894</v>
+        <v>0.1541192</v>
       </c>
       <c r="N5">
-        <v>4.444410599999999</v>
+        <v>4.405880799999999</v>
       </c>
       <c r="O5">
-        <v>1.11110265</v>
+        <v>1.1014702</v>
       </c>
       <c r="P5">
-        <v>3.33330795</v>
+        <v>3.3044106</v>
       </c>
       <c r="Q5">
-        <v>3.94330795</v>
+        <v>3.9144106</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1491857490301647</v>
+        <v>0.1499995537297095</v>
       </c>
       <c r="T5">
-        <v>0.9998192090295871</v>
+        <v>1.00768932245079</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>39.44998416809847</v>
+        <v>29.58748812607384</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1455085715805211</v>
+        <v>0.1451752166017824</v>
       </c>
       <c r="C6">
-        <v>74.57681586534576</v>
+        <v>74.04590253666746</v>
       </c>
       <c r="D6">
-        <v>70.08081586534577</v>
+        <v>70.31590253666745</v>
       </c>
       <c r="E6">
-        <v>-7.536</v>
+        <v>-6.77</v>
       </c>
       <c r="F6">
-        <v>3.064</v>
+        <v>3.83</v>
       </c>
       <c r="G6">
         <v>7.56</v>
@@ -1779,28 +1779,28 @@
         <v>4.56</v>
       </c>
       <c r="M6">
-        <v>0.1541192</v>
+        <v>0.192649</v>
       </c>
       <c r="N6">
-        <v>4.405880799999999</v>
+        <v>4.367350999999999</v>
       </c>
       <c r="O6">
-        <v>1.1014702</v>
+        <v>1.09183775</v>
       </c>
       <c r="P6">
-        <v>3.3044106</v>
+        <v>3.275513249999999</v>
       </c>
       <c r="Q6">
-        <v>3.9144106</v>
+        <v>3.88551325</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1499995537297095</v>
+        <v>0.150830491159771</v>
       </c>
       <c r="T6">
-        <v>1.00768932245079</v>
+        <v>1.015725122470334</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.58748812607384</v>
+        <v>23.66999050085907</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1451752166017824</v>
+        <v>0.1448418616230437</v>
       </c>
       <c r="C7">
-        <v>74.04590253666746</v>
+        <v>73.51657171686034</v>
       </c>
       <c r="D7">
-        <v>70.31590253666745</v>
+        <v>70.55257171686034</v>
       </c>
       <c r="E7">
-        <v>-6.77</v>
+        <v>-6.004</v>
       </c>
       <c r="F7">
-        <v>3.83</v>
+        <v>4.596</v>
       </c>
       <c r="G7">
         <v>7.56</v>
@@ -1861,28 +1861,28 @@
         <v>4.56</v>
       </c>
       <c r="M7">
-        <v>0.192649</v>
+        <v>0.2311788</v>
       </c>
       <c r="N7">
-        <v>4.367350999999999</v>
+        <v>4.328821199999999</v>
       </c>
       <c r="O7">
-        <v>1.09183775</v>
+        <v>1.0822053</v>
       </c>
       <c r="P7">
-        <v>3.275513249999999</v>
+        <v>3.246615899999999</v>
       </c>
       <c r="Q7">
-        <v>3.88551325</v>
+        <v>3.8566159</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.150830491159771</v>
+        <v>0.151679108109621</v>
       </c>
       <c r="T7">
-        <v>1.015725122470334</v>
+        <v>1.023931896958378</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.66999050085907</v>
+        <v>19.72499208404923</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1448418616230437</v>
+        <v>0.144508506644305</v>
       </c>
       <c r="C8">
-        <v>73.51657171686034</v>
+        <v>72.98883943910826</v>
       </c>
       <c r="D8">
-        <v>70.55257171686034</v>
+        <v>70.79083943910825</v>
       </c>
       <c r="E8">
-        <v>-6.004</v>
+        <v>-5.238</v>
       </c>
       <c r="F8">
-        <v>4.595999999999999</v>
+        <v>5.361999999999999</v>
       </c>
       <c r="G8">
         <v>7.56</v>
@@ -1943,28 +1943,28 @@
         <v>4.56</v>
       </c>
       <c r="M8">
-        <v>0.2311787999999999</v>
+        <v>0.2697086</v>
       </c>
       <c r="N8">
-        <v>4.328821199999999</v>
+        <v>4.290291399999999</v>
       </c>
       <c r="O8">
-        <v>1.0822053</v>
+        <v>1.07257285</v>
       </c>
       <c r="P8">
-        <v>3.246615899999999</v>
+        <v>3.217718549999999</v>
       </c>
       <c r="Q8">
-        <v>3.8566159</v>
+        <v>3.82771855</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.151679108109621</v>
+        <v>0.1525459748863495</v>
       </c>
       <c r="T8">
-        <v>1.023931896958378</v>
+        <v>1.032315161220359</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.72499208404923</v>
+        <v>16.9071360720422</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.144508506644305</v>
+        <v>0.1441751516655663</v>
       </c>
       <c r="C9">
-        <v>72.98883943910828</v>
+        <v>72.46272195391589</v>
       </c>
       <c r="D9">
-        <v>70.79083943910827</v>
+        <v>71.03072195391589</v>
       </c>
       <c r="E9">
-        <v>-5.238</v>
+        <v>-4.472</v>
       </c>
       <c r="F9">
-        <v>5.362</v>
+        <v>6.128</v>
       </c>
       <c r="G9">
         <v>7.56</v>
@@ -2025,28 +2025,28 @@
         <v>4.56</v>
       </c>
       <c r="M9">
-        <v>0.2697086</v>
+        <v>0.3082384</v>
       </c>
       <c r="N9">
-        <v>4.290291399999999</v>
+        <v>4.2517616</v>
       </c>
       <c r="O9">
-        <v>1.07257285</v>
+        <v>1.0629404</v>
       </c>
       <c r="P9">
-        <v>3.217718549999999</v>
+        <v>3.1888212</v>
       </c>
       <c r="Q9">
-        <v>3.82771855</v>
+        <v>3.7988212</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1525459748863495</v>
+        <v>0.1534316865930069</v>
       </c>
       <c r="T9">
-        <v>1.032315161220359</v>
+        <v>1.040880670357601</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.9071360720422</v>
+        <v>14.79374406303692</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1441751516655663</v>
+        <v>0.1438417966868276</v>
       </c>
       <c r="C10">
-        <v>72.46272195391589</v>
+        <v>71.93823573280324</v>
       </c>
       <c r="D10">
-        <v>71.03072195391589</v>
+        <v>71.27223573280324</v>
       </c>
       <c r="E10">
-        <v>-4.472</v>
+        <v>-3.706</v>
       </c>
       <c r="F10">
-        <v>6.128</v>
+        <v>6.893999999999999</v>
       </c>
       <c r="G10">
         <v>7.56</v>
@@ -2107,28 +2107,28 @@
         <v>4.56</v>
       </c>
       <c r="M10">
-        <v>0.3082384</v>
+        <v>0.3467682</v>
       </c>
       <c r="N10">
-        <v>4.2517616</v>
+        <v>4.2132318</v>
       </c>
       <c r="O10">
-        <v>1.0629404</v>
+        <v>1.05330795</v>
       </c>
       <c r="P10">
-        <v>3.1888212</v>
+        <v>3.15992385</v>
       </c>
       <c r="Q10">
-        <v>3.7988212</v>
+        <v>3.769923850000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1534316865930069</v>
+        <v>0.1543368644910194</v>
       </c>
       <c r="T10">
-        <v>1.040880670357601</v>
+        <v>1.049634432442914</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.79374406303692</v>
+        <v>13.14999472269949</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1438417966868276</v>
+        <v>0.143620941708089</v>
       </c>
       <c r="C11">
-        <v>71.93823573280324</v>
+        <v>71.3331504391286</v>
       </c>
       <c r="D11">
-        <v>71.27223573280324</v>
+        <v>71.4331504391286</v>
       </c>
       <c r="E11">
-        <v>-3.706</v>
+        <v>-2.940000000000001</v>
       </c>
       <c r="F11">
-        <v>6.893999999999999</v>
+        <v>7.659999999999998</v>
       </c>
       <c r="G11">
         <v>7.56</v>
@@ -2189,45 +2189,45 @@
         <v>4.56</v>
       </c>
       <c r="M11">
-        <v>0.3467682</v>
+        <v>0.3967879999999999</v>
       </c>
       <c r="N11">
-        <v>4.2132318</v>
+        <v>4.163212</v>
       </c>
       <c r="O11">
-        <v>1.05330795</v>
+        <v>1.040803</v>
       </c>
       <c r="P11">
-        <v>3.15992385</v>
+        <v>3.122409</v>
       </c>
       <c r="Q11">
-        <v>3.769923850000001</v>
+        <v>3.732409</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1543368644910194</v>
+        <v>0.1552621574534322</v>
       </c>
       <c r="T11">
-        <v>1.049634432442914</v>
+        <v>1.058582722574567</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.14999472269949</v>
+        <v>11.49228303275301</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.143620941708089</v>
+        <v>0.1432988367293503</v>
       </c>
       <c r="C12">
-        <v>71.3331504391286</v>
+        <v>70.80314272555253</v>
       </c>
       <c r="D12">
-        <v>71.4331504391286</v>
+        <v>71.66914272555253</v>
       </c>
       <c r="E12">
-        <v>-2.94</v>
+        <v>-2.173999999999999</v>
       </c>
       <c r="F12">
-        <v>7.66</v>
+        <v>8.426</v>
       </c>
       <c r="G12">
         <v>7.56</v>
@@ -2271,28 +2271,28 @@
         <v>4.56</v>
       </c>
       <c r="M12">
-        <v>0.396788</v>
+        <v>0.4364668</v>
       </c>
       <c r="N12">
-        <v>4.163212</v>
+        <v>4.1235332</v>
       </c>
       <c r="O12">
-        <v>1.040803</v>
+        <v>1.0308833</v>
       </c>
       <c r="P12">
-        <v>3.122409</v>
+        <v>3.0926499</v>
       </c>
       <c r="Q12">
-        <v>3.732409</v>
+        <v>3.7026499</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1552621574534322</v>
+        <v>0.1562082435161239</v>
       </c>
       <c r="T12">
-        <v>1.058582722574567</v>
+        <v>1.067732097877718</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.49228303275301</v>
+        <v>10.44753002977546</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1432988367293503</v>
+        <v>0.1431297317506116</v>
       </c>
       <c r="C13">
-        <v>70.80314272555253</v>
+        <v>70.16166386250457</v>
       </c>
       <c r="D13">
-        <v>71.66914272555253</v>
+        <v>71.79366386250456</v>
       </c>
       <c r="E13">
-        <v>-2.173999999999999</v>
+        <v>-1.408000000000001</v>
       </c>
       <c r="F13">
-        <v>8.426</v>
+        <v>9.191999999999998</v>
       </c>
       <c r="G13">
         <v>7.56</v>
@@ -2353,45 +2353,45 @@
         <v>4.56</v>
       </c>
       <c r="M13">
-        <v>0.4364668</v>
+        <v>0.4917719999999999</v>
       </c>
       <c r="N13">
-        <v>4.1235332</v>
+        <v>4.068228</v>
       </c>
       <c r="O13">
-        <v>1.0308833</v>
+        <v>1.017057</v>
       </c>
       <c r="P13">
-        <v>3.0926499</v>
+        <v>3.051171</v>
       </c>
       <c r="Q13">
-        <v>3.7026499</v>
+        <v>3.661171</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1562082435161239</v>
+        <v>0.1571758315347859</v>
       </c>
       <c r="T13">
-        <v>1.067732097877718</v>
+        <v>1.077089413528668</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.44753002977546</v>
+        <v>9.272589736707255</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1431297317506116</v>
+        <v>0.1428203767718729</v>
       </c>
       <c r="C14">
-        <v>70.16166386250457</v>
+        <v>69.62458203512705</v>
       </c>
       <c r="D14">
-        <v>71.79366386250456</v>
+        <v>72.02258203512704</v>
       </c>
       <c r="E14">
-        <v>-1.408000000000001</v>
+        <v>-0.6419999999999995</v>
       </c>
       <c r="F14">
-        <v>9.191999999999998</v>
+        <v>9.958</v>
       </c>
       <c r="G14">
         <v>7.56</v>
@@ -2435,28 +2435,28 @@
         <v>4.56</v>
       </c>
       <c r="M14">
-        <v>0.4917719999999999</v>
+        <v>0.532753</v>
       </c>
       <c r="N14">
-        <v>4.068228</v>
+        <v>4.027246999999999</v>
       </c>
       <c r="O14">
-        <v>1.017057</v>
+        <v>1.00681175</v>
       </c>
       <c r="P14">
-        <v>3.051171</v>
+        <v>3.020435249999999</v>
       </c>
       <c r="Q14">
-        <v>3.661171</v>
+        <v>3.63043525</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1571758315347859</v>
+        <v>0.1581656629561757</v>
       </c>
       <c r="T14">
-        <v>1.077089413528668</v>
+        <v>1.086661839884237</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.272589736707255</v>
+        <v>8.559313603114386</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1428203767718729</v>
+        <v>0.1425110217931342</v>
       </c>
       <c r="C15">
-        <v>69.62458203512705</v>
+        <v>69.08896471458874</v>
       </c>
       <c r="D15">
-        <v>72.02258203512704</v>
+        <v>72.25296471458874</v>
       </c>
       <c r="E15">
-        <v>-0.6419999999999995</v>
+        <v>0.1240000000000006</v>
       </c>
       <c r="F15">
-        <v>9.958</v>
+        <v>10.724</v>
       </c>
       <c r="G15">
         <v>7.56</v>
@@ -2517,28 +2517,28 @@
         <v>4.56</v>
       </c>
       <c r="M15">
-        <v>0.532753</v>
+        <v>0.573734</v>
       </c>
       <c r="N15">
-        <v>4.027246999999999</v>
+        <v>3.986266</v>
       </c>
       <c r="O15">
-        <v>1.00681175</v>
+        <v>0.9965664999999999</v>
       </c>
       <c r="P15">
-        <v>3.020435249999999</v>
+        <v>2.9896995</v>
       </c>
       <c r="Q15">
-        <v>3.63043525</v>
+        <v>3.5996995</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1581656629561757</v>
+        <v>0.1591785137129467</v>
       </c>
       <c r="T15">
-        <v>1.086661839884237</v>
+        <v>1.096456880806215</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.559313603114386</v>
+        <v>7.94793406003479</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1425110217931342</v>
+        <v>0.1422916668143955</v>
       </c>
       <c r="C16">
-        <v>69.08896471458874</v>
+        <v>68.4872177331345</v>
       </c>
       <c r="D16">
-        <v>72.25296471458874</v>
+        <v>72.41721773313449</v>
       </c>
       <c r="E16">
-        <v>0.1240000000000006</v>
+        <v>0.8900000000000006</v>
       </c>
       <c r="F16">
-        <v>10.724</v>
+        <v>11.49</v>
       </c>
       <c r="G16">
         <v>7.56</v>
@@ -2599,45 +2599,45 @@
         <v>4.56</v>
       </c>
       <c r="M16">
-        <v>0.573734</v>
+        <v>0.623907</v>
       </c>
       <c r="N16">
-        <v>3.986266</v>
+        <v>3.936093</v>
       </c>
       <c r="O16">
-        <v>0.9965664999999999</v>
+        <v>0.9840232499999999</v>
       </c>
       <c r="P16">
-        <v>2.9896995</v>
+        <v>2.95206975</v>
       </c>
       <c r="Q16">
-        <v>3.5996995</v>
+        <v>3.56206975</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1591785137129467</v>
+        <v>0.16021519625223</v>
       </c>
       <c r="T16">
-        <v>1.096456880806215</v>
+        <v>1.106482393279299</v>
       </c>
       <c r="U16">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>7.94793406003479</v>
+        <v>7.308781597257283</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1422916668143955</v>
+        <v>0.1419883118356568</v>
       </c>
       <c r="C17">
-        <v>68.4872177331345</v>
+        <v>67.94960435440389</v>
       </c>
       <c r="D17">
-        <v>72.41721773313449</v>
+        <v>72.64560435440389</v>
       </c>
       <c r="E17">
-        <v>0.8899999999999988</v>
+        <v>1.656000000000001</v>
       </c>
       <c r="F17">
-        <v>11.49</v>
+        <v>12.256</v>
       </c>
       <c r="G17">
         <v>7.56</v>
@@ -2681,28 +2681,28 @@
         <v>4.56</v>
       </c>
       <c r="M17">
-        <v>0.6239069999999999</v>
+        <v>0.6655008</v>
       </c>
       <c r="N17">
-        <v>3.936093</v>
+        <v>3.894499199999999</v>
       </c>
       <c r="O17">
-        <v>0.9840232499999999</v>
+        <v>0.9736247999999998</v>
       </c>
       <c r="P17">
-        <v>2.95206975</v>
+        <v>2.9208744</v>
       </c>
       <c r="Q17">
-        <v>3.56206975</v>
+        <v>3.5308744</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.16021519625223</v>
+        <v>0.1612765617091153</v>
       </c>
       <c r="T17">
-        <v>1.106482393279299</v>
+        <v>1.116746608430312</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.308781597257284</v>
+        <v>6.851982747428703</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1419883118356568</v>
+        <v>0.1416849568569181</v>
       </c>
       <c r="C18">
-        <v>67.94960435440389</v>
+        <v>67.4134360870006</v>
       </c>
       <c r="D18">
-        <v>72.64560435440389</v>
+        <v>72.87543608700061</v>
       </c>
       <c r="E18">
-        <v>1.656000000000001</v>
+        <v>2.422000000000001</v>
       </c>
       <c r="F18">
-        <v>12.256</v>
+        <v>13.022</v>
       </c>
       <c r="G18">
         <v>7.56</v>
@@ -2763,28 +2763,28 @@
         <v>4.56</v>
       </c>
       <c r="M18">
-        <v>0.6655008</v>
+        <v>0.7070946</v>
       </c>
       <c r="N18">
-        <v>3.894499199999999</v>
+        <v>3.8529054</v>
       </c>
       <c r="O18">
-        <v>0.9736247999999998</v>
+        <v>0.9632263499999999</v>
       </c>
       <c r="P18">
-        <v>2.9208744</v>
+        <v>2.88967905</v>
       </c>
       <c r="Q18">
-        <v>3.5308744</v>
+        <v>3.49967905</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1612765617091153</v>
+        <v>0.1623635022372508</v>
       </c>
       <c r="T18">
-        <v>1.116746608430312</v>
+        <v>1.127258154066893</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.851982747428703</v>
+        <v>6.448924938756426</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1416849568569181</v>
+        <v>0.1415166018781794</v>
       </c>
       <c r="C19">
-        <v>67.4134360870006</v>
+        <v>66.77561596648081</v>
       </c>
       <c r="D19">
-        <v>72.87543608700061</v>
+        <v>73.00361596648081</v>
       </c>
       <c r="E19">
-        <v>2.422000000000001</v>
+        <v>3.188000000000001</v>
       </c>
       <c r="F19">
-        <v>13.022</v>
+        <v>13.788</v>
       </c>
       <c r="G19">
         <v>7.56</v>
@@ -2845,45 +2845,45 @@
         <v>4.56</v>
       </c>
       <c r="M19">
-        <v>0.7070946</v>
+        <v>0.7624764000000001</v>
       </c>
       <c r="N19">
-        <v>3.8529054</v>
+        <v>3.797523599999999</v>
       </c>
       <c r="O19">
-        <v>0.9632263499999999</v>
+        <v>0.9493808999999999</v>
       </c>
       <c r="P19">
-        <v>2.88967905</v>
+        <v>2.848142699999999</v>
       </c>
       <c r="Q19">
-        <v>3.49967905</v>
+        <v>3.4581427</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1623635022372508</v>
+        <v>0.1634769535099749</v>
       </c>
       <c r="T19">
-        <v>1.127258154066893</v>
+        <v>1.138026078865341</v>
       </c>
       <c r="U19">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.448924938756426</v>
+        <v>5.980512970630959</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1415166018781794</v>
+        <v>0.1412207468994408</v>
       </c>
       <c r="C20">
-        <v>66.77561596648081</v>
+        <v>66.23596593702096</v>
       </c>
       <c r="D20">
-        <v>73.00361596648081</v>
+        <v>73.22996593702096</v>
       </c>
       <c r="E20">
-        <v>3.187999999999999</v>
+        <v>3.953999999999999</v>
       </c>
       <c r="F20">
-        <v>13.788</v>
+        <v>14.554</v>
       </c>
       <c r="G20">
         <v>7.56</v>
@@ -2927,28 +2927,28 @@
         <v>4.56</v>
       </c>
       <c r="M20">
-        <v>0.7624763999999999</v>
+        <v>0.8048361999999999</v>
       </c>
       <c r="N20">
-        <v>3.7975236</v>
+        <v>3.7551638</v>
       </c>
       <c r="O20">
-        <v>0.9493809</v>
+        <v>0.9387909499999999</v>
       </c>
       <c r="P20">
-        <v>2.8481427</v>
+        <v>2.81637285</v>
       </c>
       <c r="Q20">
-        <v>3.4581427</v>
+        <v>3.42637285</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1634769535099749</v>
+        <v>0.164617897406717</v>
       </c>
       <c r="T20">
-        <v>1.138026078865341</v>
+        <v>1.149059878350171</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.98051297063096</v>
+        <v>5.665749130071436</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1412207468994408</v>
+        <v>0.140924891920702</v>
       </c>
       <c r="C21">
-        <v>66.23596593702096</v>
+        <v>65.69772388321024</v>
       </c>
       <c r="D21">
-        <v>73.22996593702096</v>
+        <v>73.45772388321024</v>
       </c>
       <c r="E21">
-        <v>3.953999999999999</v>
+        <v>4.720000000000001</v>
       </c>
       <c r="F21">
-        <v>14.554</v>
+        <v>15.32</v>
       </c>
       <c r="G21">
         <v>7.56</v>
@@ -3009,28 +3009,28 @@
         <v>4.56</v>
       </c>
       <c r="M21">
-        <v>0.8048361999999999</v>
+        <v>0.8471960000000001</v>
       </c>
       <c r="N21">
-        <v>3.7551638</v>
+        <v>3.712803999999999</v>
       </c>
       <c r="O21">
-        <v>0.9387909499999999</v>
+        <v>0.9282009999999998</v>
       </c>
       <c r="P21">
-        <v>2.81637285</v>
+        <v>2.784603</v>
       </c>
       <c r="Q21">
-        <v>3.42637285</v>
+        <v>3.394603</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.164617897406717</v>
+        <v>0.1657873649008776</v>
       </c>
       <c r="T21">
-        <v>1.149059878350171</v>
+        <v>1.160369522822122</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.665749130071436</v>
+        <v>5.382461673567863</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.140924891920702</v>
+        <v>0.1406290369419634</v>
       </c>
       <c r="C22">
-        <v>65.69772388321024</v>
+        <v>65.16090298318319</v>
       </c>
       <c r="D22">
-        <v>73.45772388321024</v>
+        <v>73.68690298318319</v>
       </c>
       <c r="E22">
-        <v>4.720000000000001</v>
+        <v>5.486000000000002</v>
       </c>
       <c r="F22">
-        <v>15.32</v>
+        <v>16.086</v>
       </c>
       <c r="G22">
         <v>7.56</v>
@@ -3091,28 +3091,28 @@
         <v>4.56</v>
       </c>
       <c r="M22">
-        <v>0.8471960000000001</v>
+        <v>0.8895558000000001</v>
       </c>
       <c r="N22">
-        <v>3.712803999999999</v>
+        <v>3.670444199999999</v>
       </c>
       <c r="O22">
-        <v>0.9282009999999998</v>
+        <v>0.9176110499999999</v>
       </c>
       <c r="P22">
-        <v>2.784603</v>
+        <v>2.75283315</v>
       </c>
       <c r="Q22">
-        <v>3.394603</v>
+        <v>3.36283315</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1657873649008776</v>
+        <v>0.1669864391670422</v>
       </c>
       <c r="T22">
-        <v>1.160369522822122</v>
+        <v>1.171965487407286</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.382461673567863</v>
+        <v>5.126153974826535</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1406290369419634</v>
+        <v>0.1403331819632247</v>
       </c>
       <c r="C23">
-        <v>65.16090298318319</v>
+        <v>64.6255165800458</v>
       </c>
       <c r="D23">
-        <v>73.68690298318319</v>
+        <v>73.9175165800458</v>
       </c>
       <c r="E23">
-        <v>5.485999999999999</v>
+        <v>6.252000000000001</v>
       </c>
       <c r="F23">
-        <v>16.086</v>
+        <v>16.852</v>
       </c>
       <c r="G23">
         <v>7.56</v>
@@ -3173,28 +3173,28 @@
         <v>4.56</v>
       </c>
       <c r="M23">
-        <v>0.8895557999999999</v>
+        <v>0.9319156000000001</v>
       </c>
       <c r="N23">
-        <v>3.670444199999999</v>
+        <v>3.6280844</v>
       </c>
       <c r="O23">
-        <v>0.9176110499999999</v>
+        <v>0.9070210999999999</v>
       </c>
       <c r="P23">
-        <v>2.75283315</v>
+        <v>2.7210633</v>
       </c>
       <c r="Q23">
-        <v>3.36283315</v>
+        <v>3.3310633</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1669864391670422</v>
+        <v>0.1682162589272111</v>
       </c>
       <c r="T23">
-        <v>1.171965487407286</v>
+        <v>1.183858784417711</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.126153974826537</v>
+        <v>4.893146975970785</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1403331819632247</v>
+        <v>0.140037326984486</v>
       </c>
       <c r="C24">
-        <v>64.6255165800458</v>
+        <v>64.09157818446512</v>
       </c>
       <c r="D24">
-        <v>73.9175165800458</v>
+        <v>74.14957818446511</v>
       </c>
       <c r="E24">
-        <v>6.252000000000001</v>
+        <v>7.017999999999999</v>
       </c>
       <c r="F24">
-        <v>16.852</v>
+        <v>17.618</v>
       </c>
       <c r="G24">
         <v>7.56</v>
@@ -3255,28 +3255,28 @@
         <v>4.56</v>
       </c>
       <c r="M24">
-        <v>0.9319156000000001</v>
+        <v>0.9742753999999999</v>
       </c>
       <c r="N24">
-        <v>3.6280844</v>
+        <v>3.5857246</v>
       </c>
       <c r="O24">
-        <v>0.9070210999999999</v>
+        <v>0.89643115</v>
       </c>
       <c r="P24">
-        <v>2.7210633</v>
+        <v>2.68929345</v>
       </c>
       <c r="Q24">
-        <v>3.3310633</v>
+        <v>3.29929345</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1682162589272111</v>
+        <v>0.169478022057774</v>
       </c>
       <c r="T24">
-        <v>1.183858784417711</v>
+        <v>1.196060998233602</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.893146975970785</v>
+        <v>4.680401455276403</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.140037326984486</v>
+        <v>0.1401914720057473</v>
       </c>
       <c r="C25">
-        <v>64.09157818446512</v>
+        <v>63.20448897944598</v>
       </c>
       <c r="D25">
-        <v>74.14957818446511</v>
+        <v>74.02848897944598</v>
       </c>
       <c r="E25">
-        <v>7.017999999999999</v>
+        <v>7.784000000000001</v>
       </c>
       <c r="F25">
-        <v>17.618</v>
+        <v>18.384</v>
       </c>
       <c r="G25">
         <v>7.56</v>
@@ -3337,45 +3337,45 @@
         <v>4.56</v>
       </c>
       <c r="M25">
-        <v>0.9742753999999999</v>
+        <v>1.0625952</v>
       </c>
       <c r="N25">
-        <v>3.5857246</v>
+        <v>3.4974048</v>
       </c>
       <c r="O25">
-        <v>0.89643115</v>
+        <v>0.8743511999999999</v>
       </c>
       <c r="P25">
-        <v>2.68929345</v>
+        <v>2.6230536</v>
       </c>
       <c r="Q25">
-        <v>3.29929345</v>
+        <v>3.2330536</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.169478022057774</v>
+        <v>0.1707729894812464</v>
       </c>
       <c r="T25">
-        <v>1.196060998233602</v>
+        <v>1.208584322939384</v>
       </c>
       <c r="U25">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.680401455276403</v>
+        <v>4.291380198216592</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1401914720057473</v>
+        <v>0.1399143670270086</v>
       </c>
       <c r="C26">
-        <v>63.20448897944598</v>
+        <v>62.65645424354661</v>
       </c>
       <c r="D26">
-        <v>74.02848897944598</v>
+        <v>74.24645424354661</v>
       </c>
       <c r="E26">
-        <v>7.783999999999997</v>
+        <v>8.549999999999999</v>
       </c>
       <c r="F26">
-        <v>18.384</v>
+        <v>19.15</v>
       </c>
       <c r="G26">
         <v>7.56</v>
@@ -3419,28 +3419,28 @@
         <v>4.56</v>
       </c>
       <c r="M26">
-        <v>1.0625952</v>
+        <v>1.10687</v>
       </c>
       <c r="N26">
-        <v>3.4974048</v>
+        <v>3.45313</v>
       </c>
       <c r="O26">
-        <v>0.8743512</v>
+        <v>0.8632825</v>
       </c>
       <c r="P26">
-        <v>2.6230536</v>
+        <v>2.5898475</v>
       </c>
       <c r="Q26">
-        <v>3.2330536</v>
+        <v>3.1998475</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1707729894812464</v>
+        <v>0.1721024893693448</v>
       </c>
       <c r="T26">
-        <v>1.208584322939384</v>
+        <v>1.221441602970654</v>
       </c>
       <c r="U26">
         <v>0.0578</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.291380198216594</v>
+        <v>4.119724990287929</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1399143670270086</v>
+        <v>0.1403197620482699</v>
       </c>
       <c r="C27">
-        <v>62.65645424354661</v>
+        <v>61.57201138837664</v>
       </c>
       <c r="D27">
-        <v>74.24645424354661</v>
+        <v>73.92801138837663</v>
       </c>
       <c r="E27">
-        <v>8.549999999999999</v>
+        <v>9.316000000000001</v>
       </c>
       <c r="F27">
-        <v>19.15</v>
+        <v>19.916</v>
       </c>
       <c r="G27">
         <v>7.56</v>
@@ -3501,45 +3501,45 @@
         <v>4.56</v>
       </c>
       <c r="M27">
-        <v>1.10687</v>
+        <v>1.2208508</v>
       </c>
       <c r="N27">
-        <v>3.45313</v>
+        <v>3.3391492</v>
       </c>
       <c r="O27">
-        <v>0.8632825</v>
+        <v>0.8347872999999999</v>
       </c>
       <c r="P27">
-        <v>2.5898475</v>
+        <v>2.5043619</v>
       </c>
       <c r="Q27">
-        <v>3.1998475</v>
+        <v>3.1143619</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1721024893693448</v>
+        <v>0.1734679216868513</v>
       </c>
       <c r="T27">
-        <v>1.221441602970654</v>
+        <v>1.234646377056824</v>
       </c>
       <c r="U27">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.119724990287929</v>
+        <v>3.735100144915332</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1403197620482699</v>
+        <v>0.1400689070695312</v>
       </c>
       <c r="C28">
-        <v>61.57201138837664</v>
+        <v>61.00273807484756</v>
       </c>
       <c r="D28">
-        <v>73.92801138837663</v>
+        <v>74.12473807484756</v>
       </c>
       <c r="E28">
-        <v>9.316000000000001</v>
+        <v>10.082</v>
       </c>
       <c r="F28">
-        <v>19.916</v>
+        <v>20.682</v>
       </c>
       <c r="G28">
         <v>7.56</v>
@@ -3583,28 +3583,28 @@
         <v>4.56</v>
       </c>
       <c r="M28">
-        <v>1.2208508</v>
+        <v>1.2678066</v>
       </c>
       <c r="N28">
-        <v>3.3391492</v>
+        <v>3.292193399999999</v>
       </c>
       <c r="O28">
-        <v>0.8347872999999999</v>
+        <v>0.8230483499999999</v>
       </c>
       <c r="P28">
-        <v>2.5043619</v>
+        <v>2.46914505</v>
       </c>
       <c r="Q28">
-        <v>3.1143619</v>
+        <v>3.07914505</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1734679216868513</v>
+        <v>0.1748707631089469</v>
       </c>
       <c r="T28">
-        <v>1.234646377056824</v>
+        <v>1.248212925775491</v>
       </c>
       <c r="U28">
         <v>0.0613</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.735100144915332</v>
+        <v>3.596763102511061</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1400689070695312</v>
+        <v>0.1404060520907925</v>
       </c>
       <c r="C29">
-        <v>61.00273807484756</v>
+        <v>59.97258175670577</v>
       </c>
       <c r="D29">
-        <v>74.12473807484756</v>
+        <v>73.86058175670577</v>
       </c>
       <c r="E29">
-        <v>10.082</v>
+        <v>10.848</v>
       </c>
       <c r="F29">
-        <v>20.682</v>
+        <v>21.448</v>
       </c>
       <c r="G29">
         <v>7.56</v>
@@ -3665,45 +3665,45 @@
         <v>4.56</v>
       </c>
       <c r="M29">
-        <v>1.2678066</v>
+        <v>1.3748168</v>
       </c>
       <c r="N29">
-        <v>3.292193399999999</v>
+        <v>3.1851832</v>
       </c>
       <c r="O29">
-        <v>0.8230483499999999</v>
+        <v>0.7962957999999999</v>
       </c>
       <c r="P29">
-        <v>2.46914505</v>
+        <v>2.3888874</v>
       </c>
       <c r="Q29">
-        <v>3.07914505</v>
+        <v>2.9988874</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1748707631089469</v>
+        <v>0.176312572348323</v>
       </c>
       <c r="T29">
-        <v>1.248212925775491</v>
+        <v>1.262156323069676</v>
       </c>
       <c r="U29">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.596763102511061</v>
+        <v>3.316805555474736</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1404060520907925</v>
+        <v>0.1401761971120539</v>
       </c>
       <c r="C30">
-        <v>59.97258175670577</v>
+        <v>59.38647057368318</v>
       </c>
       <c r="D30">
-        <v>73.86058175670577</v>
+        <v>74.04047057368318</v>
       </c>
       <c r="E30">
-        <v>10.848</v>
+        <v>11.614</v>
       </c>
       <c r="F30">
-        <v>21.448</v>
+        <v>22.214</v>
       </c>
       <c r="G30">
         <v>7.56</v>
@@ -3747,28 +3747,28 @@
         <v>4.56</v>
       </c>
       <c r="M30">
-        <v>1.3748168</v>
+        <v>1.4239174</v>
       </c>
       <c r="N30">
-        <v>3.1851832</v>
+        <v>3.136082599999999</v>
       </c>
       <c r="O30">
-        <v>0.7962957999999999</v>
+        <v>0.7840206499999998</v>
       </c>
       <c r="P30">
-        <v>2.3888874</v>
+        <v>2.35206195</v>
       </c>
       <c r="Q30">
-        <v>2.9988874</v>
+        <v>2.96206195</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.176312572348323</v>
+        <v>0.1777949959324702</v>
       </c>
       <c r="T30">
-        <v>1.262156323069676</v>
+        <v>1.276492492118627</v>
       </c>
       <c r="U30">
         <v>0.0641</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.316805555474736</v>
+        <v>3.202432950113538</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1401761971120539</v>
+        <v>0.1399463421333152</v>
       </c>
       <c r="C31">
-        <v>59.38647057368318</v>
+        <v>58.80123777508351</v>
       </c>
       <c r="D31">
-        <v>74.04047057368318</v>
+        <v>74.22123777508351</v>
       </c>
       <c r="E31">
-        <v>11.614</v>
+        <v>12.38</v>
       </c>
       <c r="F31">
-        <v>22.214</v>
+        <v>22.98</v>
       </c>
       <c r="G31">
         <v>7.56</v>
@@ -3829,28 +3829,28 @@
         <v>4.56</v>
       </c>
       <c r="M31">
-        <v>1.4239174</v>
+        <v>1.473018</v>
       </c>
       <c r="N31">
-        <v>3.1360826</v>
+        <v>3.086982</v>
       </c>
       <c r="O31">
-        <v>0.78402065</v>
+        <v>0.7717455</v>
       </c>
       <c r="P31">
-        <v>2.35206195</v>
+        <v>2.3152365</v>
       </c>
       <c r="Q31">
-        <v>2.96206195</v>
+        <v>2.9252365</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1777949959324702</v>
+        <v>0.1793197744761645</v>
       </c>
       <c r="T31">
-        <v>1.276492492118627</v>
+        <v>1.291238265997549</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.202432950113539</v>
+        <v>3.095685185109754</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1399463421333152</v>
+        <v>0.1415299871545765</v>
       </c>
       <c r="C32">
-        <v>58.80123777508351</v>
+        <v>56.80740836480095</v>
       </c>
       <c r="D32">
-        <v>74.22123777508351</v>
+        <v>72.99340836480094</v>
       </c>
       <c r="E32">
-        <v>12.38</v>
+        <v>13.146</v>
       </c>
       <c r="F32">
-        <v>22.98</v>
+        <v>23.746</v>
       </c>
       <c r="G32">
         <v>7.56</v>
@@ -3911,45 +3911,45 @@
         <v>4.56</v>
       </c>
       <c r="M32">
-        <v>1.473018</v>
+        <v>1.7073374</v>
       </c>
       <c r="N32">
-        <v>3.086982</v>
+        <v>2.852662599999999</v>
       </c>
       <c r="O32">
-        <v>0.7717455</v>
+        <v>0.7131656499999999</v>
       </c>
       <c r="P32">
-        <v>2.3152365</v>
+        <v>2.13949695</v>
       </c>
       <c r="Q32">
-        <v>2.9252365</v>
+        <v>2.74949695</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1793197744761645</v>
+        <v>0.1808887494993862</v>
       </c>
       <c r="T32">
-        <v>1.291238265997549</v>
+        <v>1.306411453612091</v>
       </c>
       <c r="U32">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.095685185109754</v>
+        <v>2.67082534477368</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1415299871545765</v>
+        <v>0.1413586321758378</v>
       </c>
       <c r="C33">
-        <v>56.80740836480095</v>
+        <v>56.17229956378124</v>
       </c>
       <c r="D33">
-        <v>72.99340836480094</v>
+        <v>73.12429956378124</v>
       </c>
       <c r="E33">
-        <v>13.146</v>
+        <v>13.912</v>
       </c>
       <c r="F33">
-        <v>23.746</v>
+        <v>24.512</v>
       </c>
       <c r="G33">
         <v>7.56</v>
@@ -3993,28 +3993,28 @@
         <v>4.56</v>
       </c>
       <c r="M33">
-        <v>1.7073374</v>
+        <v>1.7624128</v>
       </c>
       <c r="N33">
-        <v>2.852662599999999</v>
+        <v>2.7975872</v>
       </c>
       <c r="O33">
-        <v>0.7131656499999999</v>
+        <v>0.6993967999999999</v>
       </c>
       <c r="P33">
-        <v>2.13949695</v>
+        <v>2.0981904</v>
       </c>
       <c r="Q33">
-        <v>2.74949695</v>
+        <v>2.7081904</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1808887494993862</v>
+        <v>0.1825038708468203</v>
       </c>
       <c r="T33">
-        <v>1.306411453612091</v>
+        <v>1.322030911450591</v>
       </c>
       <c r="U33">
         <v>0.07190000000000001</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.67082534477368</v>
+        <v>2.587362052749503</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1413586321758378</v>
+        <v>0.1411872771970991</v>
       </c>
       <c r="C34">
-        <v>56.17229956378124</v>
+        <v>55.53766103215759</v>
       </c>
       <c r="D34">
-        <v>73.12429956378124</v>
+        <v>73.25566103215759</v>
       </c>
       <c r="E34">
-        <v>13.912</v>
+        <v>14.678</v>
       </c>
       <c r="F34">
-        <v>24.512</v>
+        <v>25.278</v>
       </c>
       <c r="G34">
         <v>7.56</v>
@@ -4075,28 +4075,28 @@
         <v>4.56</v>
       </c>
       <c r="M34">
-        <v>1.7624128</v>
+        <v>1.8174882</v>
       </c>
       <c r="N34">
-        <v>2.7975872</v>
+        <v>2.742511799999999</v>
       </c>
       <c r="O34">
-        <v>0.6993967999999999</v>
+        <v>0.6856279499999999</v>
       </c>
       <c r="P34">
-        <v>2.0981904</v>
+        <v>2.05688385</v>
       </c>
       <c r="Q34">
-        <v>2.7081904</v>
+        <v>2.66688385</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1825038708468203</v>
+        <v>0.1841672047717897</v>
       </c>
       <c r="T34">
-        <v>1.322030911450591</v>
+        <v>1.338116621761881</v>
       </c>
       <c r="U34">
         <v>0.07190000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.587362052749503</v>
+        <v>2.508957142060124</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1411872771970991</v>
+        <v>0.1420104222183604</v>
       </c>
       <c r="C35">
-        <v>55.53766103215759</v>
+        <v>54.14490946754053</v>
       </c>
       <c r="D35">
-        <v>73.25566103215759</v>
+        <v>72.62890946754052</v>
       </c>
       <c r="E35">
-        <v>14.678</v>
+        <v>15.444</v>
       </c>
       <c r="F35">
-        <v>25.278</v>
+        <v>26.044</v>
       </c>
       <c r="G35">
         <v>7.56</v>
@@ -4157,45 +4157,45 @@
         <v>4.56</v>
       </c>
       <c r="M35">
-        <v>1.8174882</v>
+        <v>1.9741352</v>
       </c>
       <c r="N35">
-        <v>2.742511799999999</v>
+        <v>2.5858648</v>
       </c>
       <c r="O35">
-        <v>0.6856279499999999</v>
+        <v>0.6464661999999999</v>
       </c>
       <c r="P35">
-        <v>2.05688385</v>
+        <v>1.9393986</v>
       </c>
       <c r="Q35">
-        <v>2.66688385</v>
+        <v>2.5493986</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1841672047717897</v>
+        <v>0.1858809427550915</v>
       </c>
       <c r="T35">
-        <v>1.338116621761881</v>
+        <v>1.35468977784018</v>
       </c>
       <c r="U35">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.508957142060124</v>
+        <v>2.309872191124498</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1420104222183604</v>
+        <v>0.1418683172396217</v>
       </c>
       <c r="C36">
-        <v>54.14490946754053</v>
+        <v>53.48634269768608</v>
       </c>
       <c r="D36">
-        <v>72.62890946754052</v>
+        <v>72.73634269768608</v>
       </c>
       <c r="E36">
-        <v>15.444</v>
+        <v>16.21</v>
       </c>
       <c r="F36">
-        <v>26.044</v>
+        <v>26.81</v>
       </c>
       <c r="G36">
         <v>7.56</v>
@@ -4239,28 +4239,28 @@
         <v>4.56</v>
       </c>
       <c r="M36">
-        <v>1.9741352</v>
+        <v>2.032198</v>
       </c>
       <c r="N36">
-        <v>2.5858648</v>
+        <v>2.527801999999999</v>
       </c>
       <c r="O36">
-        <v>0.6464661999999999</v>
+        <v>0.6319504999999999</v>
       </c>
       <c r="P36">
-        <v>1.9393986</v>
+        <v>1.8958515</v>
       </c>
       <c r="Q36">
-        <v>2.5493986</v>
+        <v>2.5058515</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1858809427550915</v>
+        <v>0.1876474111378796</v>
       </c>
       <c r="T36">
-        <v>1.35468977784018</v>
+        <v>1.371772877182427</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.309872191124498</v>
+        <v>2.243875842806655</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1418683172396217</v>
+        <v>0.141726212260883</v>
       </c>
       <c r="C37">
-        <v>53.48634269768608</v>
+        <v>52.82809423075479</v>
       </c>
       <c r="D37">
-        <v>72.73634269768608</v>
+        <v>72.84409423075479</v>
       </c>
       <c r="E37">
-        <v>16.21</v>
+        <v>16.976</v>
       </c>
       <c r="F37">
-        <v>26.81</v>
+        <v>27.576</v>
       </c>
       <c r="G37">
         <v>7.56</v>
@@ -4321,28 +4321,28 @@
         <v>4.56</v>
       </c>
       <c r="M37">
-        <v>2.032198</v>
+        <v>2.0902608</v>
       </c>
       <c r="N37">
-        <v>2.527801999999999</v>
+        <v>2.469739199999999</v>
       </c>
       <c r="O37">
-        <v>0.6319504999999999</v>
+        <v>0.6174347999999998</v>
       </c>
       <c r="P37">
-        <v>1.8958515</v>
+        <v>1.8523044</v>
       </c>
       <c r="Q37">
-        <v>2.5058515</v>
+        <v>2.4623044</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1876474111378796</v>
+        <v>0.1894690816576297</v>
       </c>
       <c r="T37">
-        <v>1.371772877182427</v>
+        <v>1.389389823379119</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.243875842806655</v>
+        <v>2.181545958284248</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.141726212260883</v>
+        <v>0.1415841072821444</v>
       </c>
       <c r="C38">
-        <v>52.8280942307548</v>
+        <v>52.17016548344608</v>
       </c>
       <c r="D38">
-        <v>72.84409423075479</v>
+        <v>72.95216548344608</v>
       </c>
       <c r="E38">
-        <v>16.976</v>
+        <v>17.742</v>
       </c>
       <c r="F38">
-        <v>27.576</v>
+        <v>28.342</v>
       </c>
       <c r="G38">
         <v>7.56</v>
@@ -4403,28 +4403,28 @@
         <v>4.56</v>
       </c>
       <c r="M38">
-        <v>2.0902608</v>
+        <v>2.1483236</v>
       </c>
       <c r="N38">
-        <v>2.4697392</v>
+        <v>2.4116764</v>
       </c>
       <c r="O38">
-        <v>0.6174348</v>
+        <v>0.6029190999999999</v>
       </c>
       <c r="P38">
-        <v>1.8523044</v>
+        <v>1.8087573</v>
       </c>
       <c r="Q38">
-        <v>2.4623044</v>
+        <v>2.4187573</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1894690816576297</v>
+        <v>0.1913485829875307</v>
       </c>
       <c r="T38">
-        <v>1.389389823379119</v>
+        <v>1.40756603770904</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.181545958284248</v>
+        <v>2.122585256708998</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1415841072821444</v>
+        <v>0.1414420023034056</v>
       </c>
       <c r="C39">
-        <v>52.17016548344608</v>
+        <v>51.51255788087918</v>
       </c>
       <c r="D39">
-        <v>72.95216548344608</v>
+        <v>73.06055788087917</v>
       </c>
       <c r="E39">
-        <v>17.742</v>
+        <v>18.508</v>
       </c>
       <c r="F39">
-        <v>28.342</v>
+        <v>29.108</v>
       </c>
       <c r="G39">
         <v>7.56</v>
@@ -4485,28 +4485,28 @@
         <v>4.56</v>
       </c>
       <c r="M39">
-        <v>2.1483236</v>
+        <v>2.2063864</v>
       </c>
       <c r="N39">
-        <v>2.4116764</v>
+        <v>2.3536136</v>
       </c>
       <c r="O39">
-        <v>0.6029190999999999</v>
+        <v>0.5884033999999999</v>
       </c>
       <c r="P39">
-        <v>1.8087573</v>
+        <v>1.7652102</v>
       </c>
       <c r="Q39">
-        <v>2.4187573</v>
+        <v>2.3752102</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1913485829875307</v>
+        <v>0.1932887133925898</v>
       </c>
       <c r="T39">
-        <v>1.40756603770904</v>
+        <v>1.426328581533474</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.122585256708998</v>
+        <v>2.066727749953499</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1414420023034056</v>
+        <v>0.141299897324667</v>
       </c>
       <c r="C40">
-        <v>51.51255788087918</v>
+        <v>50.85527285665557</v>
       </c>
       <c r="D40">
-        <v>73.06055788087917</v>
+        <v>73.16927285665557</v>
       </c>
       <c r="E40">
-        <v>18.508</v>
+        <v>19.274</v>
       </c>
       <c r="F40">
-        <v>29.108</v>
+        <v>29.874</v>
       </c>
       <c r="G40">
         <v>7.56</v>
@@ -4567,28 +4567,28 @@
         <v>4.56</v>
       </c>
       <c r="M40">
-        <v>2.2063864</v>
+        <v>2.2644492</v>
       </c>
       <c r="N40">
-        <v>2.3536136</v>
+        <v>2.2955508</v>
       </c>
       <c r="O40">
-        <v>0.5884033999999999</v>
+        <v>0.5738876999999999</v>
       </c>
       <c r="P40">
-        <v>1.7652102</v>
+        <v>1.7216631</v>
       </c>
       <c r="Q40">
-        <v>2.3752102</v>
+        <v>2.3316631</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1932887133925898</v>
+        <v>0.1952924546306016</v>
       </c>
       <c r="T40">
-        <v>1.426328581533474</v>
+        <v>1.445706290729201</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.066727749953499</v>
+        <v>2.013734730723922</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.141299897324667</v>
+        <v>0.1454177923459282</v>
       </c>
       <c r="C41">
-        <v>50.85527285665557</v>
+        <v>47.0646787825424</v>
       </c>
       <c r="D41">
-        <v>73.16927285665557</v>
+        <v>70.1446787825424</v>
       </c>
       <c r="E41">
-        <v>19.274</v>
+        <v>20.04</v>
       </c>
       <c r="F41">
-        <v>29.874</v>
+        <v>30.64</v>
       </c>
       <c r="G41">
         <v>7.56</v>
@@ -4649,45 +4649,45 @@
         <v>4.56</v>
       </c>
       <c r="M41">
-        <v>2.2644492</v>
+        <v>2.7576</v>
       </c>
       <c r="N41">
-        <v>2.2955508</v>
+        <v>1.8024</v>
       </c>
       <c r="O41">
-        <v>0.5738876999999999</v>
+        <v>0.4505999999999999</v>
       </c>
       <c r="P41">
-        <v>1.7216631</v>
+        <v>1.3518</v>
       </c>
       <c r="Q41">
-        <v>2.3316631</v>
+        <v>1.9618</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1952924546306016</v>
+        <v>0.1973629872432138</v>
       </c>
       <c r="T41">
-        <v>1.445706290729201</v>
+        <v>1.465729923564785</v>
       </c>
       <c r="U41">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.013734730723922</v>
+        <v>1.65361183637946</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1454177923459282</v>
+        <v>0.1453821873671896</v>
       </c>
       <c r="C42">
-        <v>47.0646787825424</v>
+        <v>46.32375856701704</v>
       </c>
       <c r="D42">
-        <v>70.1446787825424</v>
+        <v>70.16975856701704</v>
       </c>
       <c r="E42">
-        <v>20.04</v>
+        <v>20.806</v>
       </c>
       <c r="F42">
-        <v>30.64</v>
+        <v>31.406</v>
       </c>
       <c r="G42">
         <v>7.56</v>
@@ -4731,28 +4731,28 @@
         <v>4.56</v>
       </c>
       <c r="M42">
-        <v>2.7576</v>
+        <v>2.82654</v>
       </c>
       <c r="N42">
-        <v>1.8024</v>
+        <v>1.73346</v>
       </c>
       <c r="O42">
-        <v>0.4505999999999999</v>
+        <v>0.433365</v>
       </c>
       <c r="P42">
-        <v>1.3518</v>
+        <v>1.300095</v>
       </c>
       <c r="Q42">
-        <v>1.9618</v>
+        <v>1.910095</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1973629872432138</v>
+        <v>0.1995037074020163</v>
       </c>
       <c r="T42">
-        <v>1.465729923564785</v>
+        <v>1.486432323615135</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.65361183637946</v>
+        <v>1.613279840370205</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1453821873671896</v>
+        <v>0.1453465823884509</v>
       </c>
       <c r="C43">
-        <v>46.32375856701704</v>
+        <v>45.58285629214165</v>
       </c>
       <c r="D43">
-        <v>70.16975856701704</v>
+        <v>70.19485629214165</v>
       </c>
       <c r="E43">
-        <v>20.806</v>
+        <v>21.572</v>
       </c>
       <c r="F43">
-        <v>31.406</v>
+        <v>32.172</v>
       </c>
       <c r="G43">
         <v>7.56</v>
@@ -4813,28 +4813,28 @@
         <v>4.56</v>
       </c>
       <c r="M43">
-        <v>2.82654</v>
+        <v>2.89548</v>
       </c>
       <c r="N43">
-        <v>1.73346</v>
+        <v>1.66452</v>
       </c>
       <c r="O43">
-        <v>0.433365</v>
+        <v>0.4161299999999999</v>
       </c>
       <c r="P43">
-        <v>1.300095</v>
+        <v>1.24839</v>
       </c>
       <c r="Q43">
-        <v>1.910095</v>
+        <v>1.85839</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1995037074020163</v>
+        <v>0.2017182454973291</v>
       </c>
       <c r="T43">
-        <v>1.486432323615135</v>
+        <v>1.507848599529291</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.613279840370205</v>
+        <v>1.574868415599486</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1453465823884509</v>
+        <v>0.1453109774097122</v>
       </c>
       <c r="C44">
-        <v>45.58285629214166</v>
+        <v>44.84197197717361</v>
       </c>
       <c r="D44">
-        <v>70.19485629214165</v>
+        <v>70.2199719771736</v>
       </c>
       <c r="E44">
-        <v>21.572</v>
+        <v>22.33799999999999</v>
       </c>
       <c r="F44">
-        <v>32.172</v>
+        <v>32.938</v>
       </c>
       <c r="G44">
         <v>7.56</v>
@@ -4895,28 +4895,28 @@
         <v>4.56</v>
       </c>
       <c r="M44">
-        <v>2.89548</v>
+        <v>2.96442</v>
       </c>
       <c r="N44">
-        <v>1.66452</v>
+        <v>1.59558</v>
       </c>
       <c r="O44">
-        <v>0.41613</v>
+        <v>0.398895</v>
       </c>
       <c r="P44">
-        <v>1.24839</v>
+        <v>1.196685</v>
       </c>
       <c r="Q44">
-        <v>1.85839</v>
+        <v>1.806685</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2017182454973291</v>
+        <v>0.2040104866837056</v>
       </c>
       <c r="T44">
-        <v>1.507848599529291</v>
+        <v>1.530016323721135</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.574868415599486</v>
+        <v>1.53824356872508</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1453109774097122</v>
+        <v>0.1452753724309735</v>
       </c>
       <c r="C45">
-        <v>44.84197197717361</v>
+        <v>44.10110564139804</v>
       </c>
       <c r="D45">
-        <v>70.2199719771736</v>
+        <v>70.24510564139804</v>
       </c>
       <c r="E45">
-        <v>22.33799999999999</v>
+        <v>23.104</v>
       </c>
       <c r="F45">
-        <v>32.938</v>
+        <v>33.704</v>
       </c>
       <c r="G45">
         <v>7.56</v>
@@ -4977,28 +4977,28 @@
         <v>4.56</v>
       </c>
       <c r="M45">
-        <v>2.96442</v>
+        <v>3.03336</v>
       </c>
       <c r="N45">
-        <v>1.59558</v>
+        <v>1.52664</v>
       </c>
       <c r="O45">
-        <v>0.398895</v>
+        <v>0.3816599999999999</v>
       </c>
       <c r="P45">
-        <v>1.196685</v>
+        <v>1.14498</v>
       </c>
       <c r="Q45">
-        <v>1.806685</v>
+        <v>1.75498</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2040104866837056</v>
+        <v>0.2063845936267384</v>
       </c>
       <c r="T45">
-        <v>1.530016323721135</v>
+        <v>1.552975752348403</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.53824356872508</v>
+        <v>1.503283487617691</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1452753724309735</v>
+        <v>0.1671659011943928</v>
       </c>
       <c r="C46">
-        <v>44.10110564139804</v>
+        <v>30.66513417165628</v>
       </c>
       <c r="D46">
-        <v>70.24510564139804</v>
+        <v>57.57513417165628</v>
       </c>
       <c r="E46">
-        <v>23.104</v>
+        <v>23.87</v>
       </c>
       <c r="F46">
-        <v>33.704</v>
+        <v>34.47</v>
       </c>
       <c r="G46">
         <v>7.56</v>
@@ -5059,45 +5059,45 @@
         <v>4.56</v>
       </c>
       <c r="M46">
-        <v>3.03336</v>
+        <v>5.060196</v>
       </c>
       <c r="N46">
-        <v>1.52664</v>
+        <v>-0.5001960000000008</v>
       </c>
       <c r="O46">
-        <v>0.3816599999999999</v>
+        <v>-0.1250490000000002</v>
       </c>
       <c r="P46">
-        <v>1.14498</v>
+        <v>-0.3751470000000006</v>
       </c>
       <c r="Q46">
-        <v>1.75498</v>
+        <v>0.2348529999999998</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2063845936267384</v>
+        <v>0.2108880140396509</v>
       </c>
       <c r="T46">
-        <v>1.552975752348403</v>
+        <v>1.596527269626206</v>
       </c>
       <c r="U46">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.25</v>
+        <v>0.2252877161279918</v>
       </c>
       <c r="W46">
-        <v>0.0675</v>
+        <v>0.1137277632724108</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y46">
-        <v>1.503283487617691</v>
+        <v>0.9011508645119674</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1671659011943928</v>
+        <v>0.1681759011943929</v>
       </c>
       <c r="C47">
-        <v>30.66513417165628</v>
+        <v>29.42395168110203</v>
       </c>
       <c r="D47">
-        <v>57.57513417165628</v>
+        <v>57.09995168110203</v>
       </c>
       <c r="E47">
-        <v>23.87</v>
+        <v>24.636</v>
       </c>
       <c r="F47">
-        <v>34.47</v>
+        <v>35.236</v>
       </c>
       <c r="G47">
         <v>7.56</v>
@@ -5141,37 +5141,37 @@
         <v>4.56</v>
       </c>
       <c r="M47">
-        <v>5.060196</v>
+        <v>5.1726448</v>
       </c>
       <c r="N47">
-        <v>-0.5001960000000008</v>
+        <v>-0.6126448000000009</v>
       </c>
       <c r="O47">
-        <v>-0.1250490000000002</v>
+        <v>-0.1531612000000002</v>
       </c>
       <c r="P47">
-        <v>-0.3751470000000006</v>
+        <v>-0.4594836000000007</v>
       </c>
       <c r="Q47">
-        <v>0.2348529999999998</v>
+        <v>0.1505163999999997</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2108880140396509</v>
+        <v>0.2139451994848296</v>
       </c>
       <c r="T47">
-        <v>1.596527269626206</v>
+        <v>1.626092589434099</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.2252877161279918</v>
+        <v>0.2203901570817312</v>
       </c>
       <c r="W47">
-        <v>0.1137277632724108</v>
+        <v>0.1144467249404019</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.9011508645119674</v>
+        <v>0.8815606283269246</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1681759011943929</v>
+        <v>0.1691859011943928</v>
       </c>
       <c r="C48">
-        <v>29.42395168110203</v>
+        <v>28.19054859339386</v>
       </c>
       <c r="D48">
-        <v>57.09995168110203</v>
+        <v>56.63254859339387</v>
       </c>
       <c r="E48">
-        <v>24.636</v>
+        <v>25.402</v>
       </c>
       <c r="F48">
-        <v>35.236</v>
+        <v>36.002</v>
       </c>
       <c r="G48">
         <v>7.56</v>
@@ -5223,37 +5223,37 @@
         <v>4.56</v>
       </c>
       <c r="M48">
-        <v>5.1726448</v>
+        <v>5.285093600000001</v>
       </c>
       <c r="N48">
-        <v>-0.6126448000000009</v>
+        <v>-0.725093600000001</v>
       </c>
       <c r="O48">
-        <v>-0.1531612000000002</v>
+        <v>-0.1812734000000003</v>
       </c>
       <c r="P48">
-        <v>-0.4594836000000007</v>
+        <v>-0.5438202000000008</v>
       </c>
       <c r="Q48">
-        <v>0.1505163999999997</v>
+        <v>0.06617979999999957</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2139451994848296</v>
+        <v>0.2171177504185056</v>
       </c>
       <c r="T48">
-        <v>1.626092589434099</v>
+        <v>1.656773581687573</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.2203901570817312</v>
+        <v>0.2157010048033964</v>
       </c>
       <c r="W48">
-        <v>0.1144467249404019</v>
+        <v>0.1151350924948614</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8815606283269246</v>
+        <v>0.8628040192135857</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1691859011943928</v>
+        <v>0.1701959011943929</v>
       </c>
       <c r="C49">
-        <v>28.19054859339386</v>
+        <v>26.96473542004867</v>
       </c>
       <c r="D49">
-        <v>56.63254859339387</v>
+        <v>56.17273542004867</v>
       </c>
       <c r="E49">
-        <v>25.402</v>
+        <v>26.168</v>
       </c>
       <c r="F49">
-        <v>36.002</v>
+        <v>36.768</v>
       </c>
       <c r="G49">
         <v>7.56</v>
@@ -5305,37 +5305,37 @@
         <v>4.56</v>
       </c>
       <c r="M49">
-        <v>5.285093600000001</v>
+        <v>5.397542400000001</v>
       </c>
       <c r="N49">
-        <v>-0.725093600000001</v>
+        <v>-0.8375424000000011</v>
       </c>
       <c r="O49">
-        <v>-0.1812734000000003</v>
+        <v>-0.2093856000000003</v>
       </c>
       <c r="P49">
-        <v>-0.5438202000000008</v>
+        <v>-0.6281568000000008</v>
       </c>
       <c r="Q49">
-        <v>0.06617979999999957</v>
+        <v>-0.01815680000000053</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2171177504185056</v>
+        <v>0.2204123225419384</v>
       </c>
       <c r="T49">
-        <v>1.656773581687573</v>
+        <v>1.688634612104641</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.2157010048033964</v>
+        <v>0.2112072338699924</v>
       </c>
       <c r="W49">
-        <v>0.1151350924948614</v>
+        <v>0.1157947780678851</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8628040192135857</v>
+        <v>0.8448289354799694</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1701959011943928</v>
+        <v>0.1712059011943928</v>
       </c>
       <c r="C50">
-        <v>26.9647354200487</v>
+        <v>25.74632877702873</v>
       </c>
       <c r="D50">
-        <v>56.17273542004869</v>
+        <v>55.72032877702873</v>
       </c>
       <c r="E50">
-        <v>26.16799999999999</v>
+        <v>26.934</v>
       </c>
       <c r="F50">
-        <v>36.76799999999999</v>
+        <v>37.534</v>
       </c>
       <c r="G50">
         <v>7.56</v>
@@ -5387,37 +5387,37 @@
         <v>4.56</v>
       </c>
       <c r="M50">
-        <v>5.3975424</v>
+        <v>5.5099912</v>
       </c>
       <c r="N50">
-        <v>-0.8375424000000002</v>
+        <v>-0.9499912000000004</v>
       </c>
       <c r="O50">
-        <v>-0.2093856000000001</v>
+        <v>-0.2374978000000001</v>
       </c>
       <c r="P50">
-        <v>-0.6281568000000002</v>
+        <v>-0.7124934000000003</v>
       </c>
       <c r="Q50">
-        <v>-0.01815679999999986</v>
+        <v>-0.1024934</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2204123225419384</v>
+        <v>0.2238360935721725</v>
       </c>
       <c r="T50">
-        <v>1.688634612104641</v>
+        <v>1.721745094694928</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.2112072338699924</v>
+        <v>0.2068968821583599</v>
       </c>
       <c r="W50">
-        <v>0.1157947780678851</v>
+        <v>0.1164275376991528</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8448289354799695</v>
+        <v>0.8275875286334395</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1712059011943928</v>
+        <v>0.1722159011943928</v>
       </c>
       <c r="C51">
-        <v>25.74632877702873</v>
+        <v>24.5351511408842</v>
       </c>
       <c r="D51">
-        <v>55.72032877702873</v>
+        <v>55.2751511408842</v>
       </c>
       <c r="E51">
-        <v>26.934</v>
+        <v>27.7</v>
       </c>
       <c r="F51">
-        <v>37.534</v>
+        <v>38.3</v>
       </c>
       <c r="G51">
         <v>7.56</v>
@@ -5469,37 +5469,37 @@
         <v>4.56</v>
       </c>
       <c r="M51">
-        <v>5.5099912</v>
+        <v>5.62244</v>
       </c>
       <c r="N51">
-        <v>-0.9499912000000004</v>
+        <v>-1.06244</v>
       </c>
       <c r="O51">
-        <v>-0.2374978000000001</v>
+        <v>-0.2656100000000001</v>
       </c>
       <c r="P51">
-        <v>-0.7124934000000003</v>
+        <v>-0.7968300000000004</v>
       </c>
       <c r="Q51">
-        <v>-0.1024934</v>
+        <v>-0.1868300000000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2238360935721725</v>
+        <v>0.227396815443616</v>
       </c>
       <c r="T51">
-        <v>1.721745094694928</v>
+        <v>1.756179996588827</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.2068968821583599</v>
+        <v>0.2027589445151927</v>
       </c>
       <c r="W51">
-        <v>0.1164275376991528</v>
+        <v>0.1170349869451697</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8275875286334395</v>
+        <v>0.8110357780607707</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1722159011943928</v>
+        <v>0.2035206498187856</v>
       </c>
       <c r="C52">
-        <v>24.5351511408842</v>
+        <v>12.79801506181768</v>
       </c>
       <c r="D52">
-        <v>55.2751511408842</v>
+        <v>44.30401506181767</v>
       </c>
       <c r="E52">
-        <v>27.7</v>
+        <v>28.46599999999999</v>
       </c>
       <c r="F52">
-        <v>38.3</v>
+        <v>39.066</v>
       </c>
       <c r="G52">
         <v>7.56</v>
@@ -5551,45 +5551,45 @@
         <v>4.56</v>
       </c>
       <c r="M52">
-        <v>5.62244</v>
+        <v>7.844452799999999</v>
       </c>
       <c r="N52">
-        <v>-1.06244</v>
+        <v>-3.2844528</v>
       </c>
       <c r="O52">
-        <v>-0.2656100000000001</v>
+        <v>-0.8211131999999999</v>
       </c>
       <c r="P52">
-        <v>-0.7968300000000004</v>
+        <v>-2.463339599999999</v>
       </c>
       <c r="Q52">
-        <v>-0.1868300000000001</v>
+        <v>-1.853339599999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.227396815443616</v>
+        <v>0.2367248088697974</v>
       </c>
       <c r="T52">
-        <v>1.756179996588827</v>
+        <v>1.84638882224116</v>
       </c>
       <c r="U52">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.2027589445151927</v>
+        <v>0.1453256242423946</v>
       </c>
       <c r="W52">
-        <v>0.1170349869451697</v>
+        <v>0.1716186146521272</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.8110357780607707</v>
+        <v>0.5813024969695784</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2035206498187856</v>
+        <v>0.2050706498187856</v>
       </c>
       <c r="C53">
-        <v>12.79801506181768</v>
+        <v>11.60085449693047</v>
       </c>
       <c r="D53">
-        <v>44.30401506181767</v>
+        <v>43.87285449693047</v>
       </c>
       <c r="E53">
-        <v>28.46599999999999</v>
+        <v>29.232</v>
       </c>
       <c r="F53">
-        <v>39.066</v>
+        <v>39.832</v>
       </c>
       <c r="G53">
         <v>7.56</v>
@@ -5633,37 +5633,37 @@
         <v>4.56</v>
       </c>
       <c r="M53">
-        <v>7.844452799999999</v>
+        <v>7.998265600000001</v>
       </c>
       <c r="N53">
-        <v>-3.2844528</v>
+        <v>-3.438265600000001</v>
       </c>
       <c r="O53">
-        <v>-0.8211131999999999</v>
+        <v>-0.8595664000000003</v>
       </c>
       <c r="P53">
-        <v>-2.463339599999999</v>
+        <v>-2.578699200000001</v>
       </c>
       <c r="Q53">
-        <v>-1.853339599999999</v>
+        <v>-1.968699200000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2367248088697974</v>
+        <v>0.2407024090545849</v>
       </c>
       <c r="T53">
-        <v>1.84638882224116</v>
+        <v>1.884855256037851</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1453256242423946</v>
+        <v>0.1425309006992716</v>
       </c>
       <c r="W53">
-        <v>0.1716186146521272</v>
+        <v>0.1721797951395863</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5813024969695784</v>
+        <v>0.5701236027970863</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2050706498187856</v>
+        <v>0.2066206498187856</v>
       </c>
       <c r="C54">
-        <v>11.60085449693047</v>
+        <v>10.41200503980624</v>
       </c>
       <c r="D54">
-        <v>43.87285449693047</v>
+        <v>43.45000503980624</v>
       </c>
       <c r="E54">
-        <v>29.232</v>
+        <v>29.998</v>
       </c>
       <c r="F54">
-        <v>39.832</v>
+        <v>40.598</v>
       </c>
       <c r="G54">
         <v>7.56</v>
@@ -5715,37 +5715,37 @@
         <v>4.56</v>
       </c>
       <c r="M54">
-        <v>7.998265600000001</v>
+        <v>8.152078400000001</v>
       </c>
       <c r="N54">
-        <v>-3.438265600000001</v>
+        <v>-3.592078400000001</v>
       </c>
       <c r="O54">
-        <v>-0.8595664000000003</v>
+        <v>-0.8980196000000003</v>
       </c>
       <c r="P54">
-        <v>-2.578699200000001</v>
+        <v>-2.694058800000001</v>
       </c>
       <c r="Q54">
-        <v>-1.968699200000001</v>
+        <v>-2.0840588</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2407024090545849</v>
+        <v>0.2448492688217037</v>
       </c>
       <c r="T54">
-        <v>1.884855256037851</v>
+        <v>1.924958559357805</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1425309006992716</v>
+        <v>0.1398416384219268</v>
       </c>
       <c r="W54">
-        <v>0.1721797951395863</v>
+        <v>0.1727197990048771</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5701236027970863</v>
+        <v>0.5593665536877073</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2066206498187856</v>
+        <v>0.2081706498187856</v>
       </c>
       <c r="C55">
-        <v>10.41200503980624</v>
+        <v>9.23122867543951</v>
       </c>
       <c r="D55">
-        <v>43.45000503980624</v>
+        <v>43.03522867543951</v>
       </c>
       <c r="E55">
-        <v>29.998</v>
+        <v>30.764</v>
       </c>
       <c r="F55">
-        <v>40.598</v>
+        <v>41.364</v>
       </c>
       <c r="G55">
         <v>7.56</v>
@@ -5797,37 +5797,37 @@
         <v>4.56</v>
       </c>
       <c r="M55">
-        <v>8.152078400000001</v>
+        <v>8.3058912</v>
       </c>
       <c r="N55">
-        <v>-3.592078400000001</v>
+        <v>-3.7458912</v>
       </c>
       <c r="O55">
-        <v>-0.8980196000000003</v>
+        <v>-0.9364728</v>
       </c>
       <c r="P55">
-        <v>-2.694058800000001</v>
+        <v>-2.8094184</v>
       </c>
       <c r="Q55">
-        <v>-2.0840588</v>
+        <v>-2.1994184</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2448492688217037</v>
+        <v>0.2491764268395668</v>
       </c>
       <c r="T55">
-        <v>1.924958559357805</v>
+        <v>1.966805484561235</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1398416384219268</v>
+        <v>0.1372519784511504</v>
       </c>
       <c r="W55">
-        <v>0.1727197990048771</v>
+        <v>0.173239802727009</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5593665536877073</v>
+        <v>0.5490079138046018</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2081706498187856</v>
+        <v>0.2097206498187856</v>
       </c>
       <c r="C56">
-        <v>9.23122867543951</v>
+        <v>8.058296391308893</v>
       </c>
       <c r="D56">
-        <v>43.03522867543951</v>
+        <v>42.62829639130889</v>
       </c>
       <c r="E56">
-        <v>30.764</v>
+        <v>31.53</v>
       </c>
       <c r="F56">
-        <v>41.364</v>
+        <v>42.13</v>
       </c>
       <c r="G56">
         <v>7.56</v>
@@ -5879,37 +5879,37 @@
         <v>4.56</v>
       </c>
       <c r="M56">
-        <v>8.3058912</v>
+        <v>8.459704</v>
       </c>
       <c r="N56">
-        <v>-3.7458912</v>
+        <v>-3.899704000000001</v>
       </c>
       <c r="O56">
-        <v>-0.9364728</v>
+        <v>-0.9749260000000002</v>
       </c>
       <c r="P56">
-        <v>-2.8094184</v>
+        <v>-2.924778000000001</v>
       </c>
       <c r="Q56">
-        <v>-2.1994184</v>
+        <v>-2.314778</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2491764268395668</v>
+        <v>0.2536959029915572</v>
       </c>
       <c r="T56">
-        <v>1.966805484561235</v>
+        <v>2.010512273107041</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1372519784511504</v>
+        <v>0.1347564879338568</v>
       </c>
       <c r="W56">
-        <v>0.173239802727009</v>
+        <v>0.1737408972228816</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5490079138046018</v>
+        <v>0.539025951735427</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2097206498187856</v>
+        <v>0.2112706498187856</v>
       </c>
       <c r="C57">
-        <v>8.058296391308893</v>
+        <v>6.892987755735824</v>
       </c>
       <c r="D57">
-        <v>42.62829639130889</v>
+        <v>42.22898775573582</v>
       </c>
       <c r="E57">
-        <v>31.53</v>
+        <v>32.296</v>
       </c>
       <c r="F57">
-        <v>42.13</v>
+        <v>42.896</v>
       </c>
       <c r="G57">
         <v>7.56</v>
@@ -5961,37 +5961,37 @@
         <v>4.56</v>
       </c>
       <c r="M57">
-        <v>8.459704</v>
+        <v>8.613516800000001</v>
       </c>
       <c r="N57">
-        <v>-3.899704000000001</v>
+        <v>-4.053516800000001</v>
       </c>
       <c r="O57">
-        <v>-0.9749260000000002</v>
+        <v>-1.0133792</v>
       </c>
       <c r="P57">
-        <v>-2.924778000000001</v>
+        <v>-3.040137600000001</v>
       </c>
       <c r="Q57">
-        <v>-2.314778</v>
+        <v>-2.430137600000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2536959029915572</v>
+        <v>0.258420809877729</v>
       </c>
       <c r="T57">
-        <v>2.010512273107041</v>
+        <v>2.056205733859473</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1347564879338568</v>
+        <v>0.132350122077895</v>
       </c>
       <c r="W57">
-        <v>0.1737408972228816</v>
+        <v>0.1742240954867587</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.539025951735427</v>
+        <v>0.5294004883115802</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2112706498187856</v>
+        <v>0.2128206498187856</v>
       </c>
       <c r="C58">
-        <v>6.892987755735824</v>
+        <v>5.735090519720963</v>
       </c>
       <c r="D58">
-        <v>42.22898775573582</v>
+        <v>41.83709051972096</v>
       </c>
       <c r="E58">
-        <v>32.296</v>
+        <v>33.062</v>
       </c>
       <c r="F58">
-        <v>42.896</v>
+        <v>43.662</v>
       </c>
       <c r="G58">
         <v>7.56</v>
@@ -6043,37 +6043,37 @@
         <v>4.56</v>
       </c>
       <c r="M58">
-        <v>8.613516800000001</v>
+        <v>8.7673296</v>
       </c>
       <c r="N58">
-        <v>-4.053516800000001</v>
+        <v>-4.2073296</v>
       </c>
       <c r="O58">
-        <v>-1.0133792</v>
+        <v>-1.0518324</v>
       </c>
       <c r="P58">
-        <v>-3.040137600000001</v>
+        <v>-3.1554972</v>
       </c>
       <c r="Q58">
-        <v>-2.430137600000001</v>
+        <v>-2.5454972</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.258420809877729</v>
+        <v>0.2633654798748854</v>
       </c>
       <c r="T58">
-        <v>2.056205733859473</v>
+        <v>2.104024471856205</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.132350122077895</v>
+        <v>0.1300281901116162</v>
       </c>
       <c r="W58">
-        <v>0.1742240954867587</v>
+        <v>0.1746903394255875</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5294004883115802</v>
+        <v>0.5201127604464648</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2128206498187856</v>
+        <v>0.2143706498187856</v>
       </c>
       <c r="C59">
-        <v>5.735090519720963</v>
+        <v>4.584400240747236</v>
       </c>
       <c r="D59">
-        <v>41.83709051972096</v>
+        <v>41.45240024074724</v>
       </c>
       <c r="E59">
-        <v>33.062</v>
+        <v>33.828</v>
       </c>
       <c r="F59">
-        <v>43.662</v>
+        <v>44.428</v>
       </c>
       <c r="G59">
         <v>7.56</v>
@@ -6125,37 +6125,37 @@
         <v>4.56</v>
       </c>
       <c r="M59">
-        <v>8.7673296</v>
+        <v>8.921142400000001</v>
       </c>
       <c r="N59">
-        <v>-4.2073296</v>
+        <v>-4.361142400000001</v>
       </c>
       <c r="O59">
-        <v>-1.0518324</v>
+        <v>-1.0902856</v>
       </c>
       <c r="P59">
-        <v>-3.1554972</v>
+        <v>-3.270856800000001</v>
       </c>
       <c r="Q59">
-        <v>-2.5454972</v>
+        <v>-2.6608568</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2633654798748854</v>
+        <v>0.268545610348097</v>
       </c>
       <c r="T59">
-        <v>2.104024471856205</v>
+        <v>2.154120292614687</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1300281901116162</v>
+        <v>0.1277863247648642</v>
       </c>
       <c r="W59">
-        <v>0.1746903394255875</v>
+        <v>0.1751405059872153</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5201127604464648</v>
+        <v>0.5111452990594567</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2143706498187856</v>
+        <v>0.2159206498187856</v>
       </c>
       <c r="C60">
-        <v>4.584400240747271</v>
+        <v>3.440719927148649</v>
       </c>
       <c r="D60">
-        <v>41.45240024074726</v>
+        <v>41.07471992714864</v>
       </c>
       <c r="E60">
-        <v>33.82799999999999</v>
+        <v>34.59399999999999</v>
       </c>
       <c r="F60">
-        <v>44.42799999999999</v>
+        <v>45.194</v>
       </c>
       <c r="G60">
         <v>7.56</v>
@@ -6207,37 +6207,37 @@
         <v>4.56</v>
       </c>
       <c r="M60">
-        <v>8.921142399999999</v>
+        <v>9.0749552</v>
       </c>
       <c r="N60">
-        <v>-4.361142399999999</v>
+        <v>-4.5149552</v>
       </c>
       <c r="O60">
-        <v>-1.0902856</v>
+        <v>-1.1287388</v>
       </c>
       <c r="P60">
-        <v>-3.2708568</v>
+        <v>-3.3862164</v>
       </c>
       <c r="Q60">
-        <v>-2.660856799999999</v>
+        <v>-2.7762164</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2685456103480969</v>
+        <v>0.2739784301126847</v>
       </c>
       <c r="T60">
-        <v>2.154120292614686</v>
+        <v>2.206659811946751</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1277863247648642</v>
+        <v>0.1256204548535953</v>
       </c>
       <c r="W60">
-        <v>0.1751405059872153</v>
+        <v>0.1755754126653981</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5111452990594567</v>
+        <v>0.5024818194143812</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2159206498187856</v>
+        <v>0.2395822241624014</v>
       </c>
       <c r="C61">
-        <v>3.440719927148649</v>
+        <v>-2.340665479847821</v>
       </c>
       <c r="D61">
-        <v>41.07471992714864</v>
+        <v>36.05933452015217</v>
       </c>
       <c r="E61">
-        <v>34.59399999999999</v>
+        <v>35.35999999999999</v>
       </c>
       <c r="F61">
-        <v>45.194</v>
+        <v>45.95999999999999</v>
       </c>
       <c r="G61">
         <v>7.56</v>
@@ -6289,45 +6289,45 @@
         <v>4.56</v>
       </c>
       <c r="M61">
-        <v>9.0749552</v>
+        <v>10.837368</v>
       </c>
       <c r="N61">
-        <v>-4.5149552</v>
+        <v>-6.277368</v>
       </c>
       <c r="O61">
-        <v>-1.1287388</v>
+        <v>-1.569342</v>
       </c>
       <c r="P61">
-        <v>-3.3862164</v>
+        <v>-4.708026</v>
       </c>
       <c r="Q61">
-        <v>-2.7762164</v>
+        <v>-4.098026</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2739784301126847</v>
+        <v>0.2824618267245415</v>
       </c>
       <c r="T61">
-        <v>2.206659811946751</v>
+        <v>2.288700740894089</v>
       </c>
       <c r="U61">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1256204548535953</v>
+        <v>0.1051915926450038</v>
       </c>
       <c r="W61">
-        <v>0.1755754126653981</v>
+        <v>0.2109958224543081</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.5024818194143812</v>
+        <v>0.4207663705800153</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2395822241624014</v>
+        <v>0.2414822241624015</v>
       </c>
       <c r="C62">
-        <v>-2.340665479847821</v>
+        <v>-3.456787908604724</v>
       </c>
       <c r="D62">
-        <v>36.05933452015217</v>
+        <v>35.70921209139527</v>
       </c>
       <c r="E62">
-        <v>35.35999999999999</v>
+        <v>36.12599999999999</v>
       </c>
       <c r="F62">
-        <v>45.95999999999999</v>
+        <v>46.72599999999999</v>
       </c>
       <c r="G62">
         <v>7.56</v>
@@ -6371,37 +6371,37 @@
         <v>4.56</v>
       </c>
       <c r="M62">
-        <v>10.837368</v>
+        <v>11.0179908</v>
       </c>
       <c r="N62">
-        <v>-6.277368</v>
+        <v>-6.457990799999998</v>
       </c>
       <c r="O62">
-        <v>-1.569342</v>
+        <v>-1.6144977</v>
       </c>
       <c r="P62">
-        <v>-4.708026</v>
+        <v>-4.843493099999999</v>
       </c>
       <c r="Q62">
-        <v>-4.098026</v>
+        <v>-4.233493099999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2824618267245415</v>
+        <v>0.2885300786918375</v>
       </c>
       <c r="T62">
-        <v>2.288700740894089</v>
+        <v>2.347385375275989</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1051915926450038</v>
+        <v>0.1034671403065612</v>
       </c>
       <c r="W62">
-        <v>0.2109958224543081</v>
+        <v>0.2114024483157129</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4207663705800153</v>
+        <v>0.4138685612262447</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2414822241624015</v>
+        <v>0.2433822241624015</v>
       </c>
       <c r="C63">
-        <v>-3.456787908604724</v>
+        <v>-4.566176607974171</v>
       </c>
       <c r="D63">
-        <v>35.70921209139527</v>
+        <v>35.36582339202582</v>
       </c>
       <c r="E63">
-        <v>36.12599999999999</v>
+        <v>36.892</v>
       </c>
       <c r="F63">
-        <v>46.72599999999999</v>
+        <v>47.492</v>
       </c>
       <c r="G63">
         <v>7.56</v>
@@ -6453,37 +6453,37 @@
         <v>4.56</v>
       </c>
       <c r="M63">
-        <v>11.0179908</v>
+        <v>11.1986136</v>
       </c>
       <c r="N63">
-        <v>-6.457990799999998</v>
+        <v>-6.6386136</v>
       </c>
       <c r="O63">
-        <v>-1.6144977</v>
+        <v>-1.6596534</v>
       </c>
       <c r="P63">
-        <v>-4.843493099999999</v>
+        <v>-4.9789602</v>
       </c>
       <c r="Q63">
-        <v>-4.233493099999999</v>
+        <v>-4.3689602</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2885300786918375</v>
+        <v>0.2949177123416227</v>
       </c>
       <c r="T63">
-        <v>2.347385375275989</v>
+        <v>2.409158674625357</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1034671403065612</v>
+        <v>0.1017983154629069</v>
       </c>
       <c r="W63">
-        <v>0.2114024483157129</v>
+        <v>0.2117959572138466</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4138685612262447</v>
+        <v>0.4071932618516277</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2433822241624015</v>
+        <v>0.2452822241624015</v>
       </c>
       <c r="C64">
-        <v>-4.566176607974171</v>
+        <v>-5.669023987368462</v>
       </c>
       <c r="D64">
-        <v>35.36582339202582</v>
+        <v>35.02897601263153</v>
       </c>
       <c r="E64">
-        <v>36.892</v>
+        <v>37.65799999999999</v>
       </c>
       <c r="F64">
-        <v>47.492</v>
+        <v>48.258</v>
       </c>
       <c r="G64">
         <v>7.56</v>
@@ -6535,37 +6535,37 @@
         <v>4.56</v>
       </c>
       <c r="M64">
-        <v>11.1986136</v>
+        <v>11.3792364</v>
       </c>
       <c r="N64">
-        <v>-6.6386136</v>
+        <v>-6.8192364</v>
       </c>
       <c r="O64">
-        <v>-1.6596534</v>
+        <v>-1.7048091</v>
       </c>
       <c r="P64">
-        <v>-4.9789602</v>
+        <v>-5.1144273</v>
       </c>
       <c r="Q64">
-        <v>-4.3689602</v>
+        <v>-4.5044273</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2949177123416227</v>
+        <v>0.3016506234859909</v>
       </c>
       <c r="T64">
-        <v>2.409158674625357</v>
+        <v>2.474271071236853</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1017983154629069</v>
+        <v>0.1001824691857179</v>
       </c>
       <c r="W64">
-        <v>0.2117959572138466</v>
+        <v>0.2121769737660077</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4071932618516277</v>
+        <v>0.4007298767428717</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2452822241624015</v>
+        <v>0.2471822241624015</v>
       </c>
       <c r="C65">
-        <v>-5.669023987368462</v>
+        <v>-6.765515194826428</v>
       </c>
       <c r="D65">
-        <v>35.02897601263153</v>
+        <v>34.69848480517357</v>
       </c>
       <c r="E65">
-        <v>37.65799999999999</v>
+        <v>38.424</v>
       </c>
       <c r="F65">
-        <v>48.258</v>
+        <v>49.024</v>
       </c>
       <c r="G65">
         <v>7.56</v>
@@ -6617,37 +6617,37 @@
         <v>4.56</v>
       </c>
       <c r="M65">
-        <v>11.3792364</v>
+        <v>11.5598592</v>
       </c>
       <c r="N65">
-        <v>-6.8192364</v>
+        <v>-6.9998592</v>
       </c>
       <c r="O65">
-        <v>-1.7048091</v>
+        <v>-1.7499648</v>
       </c>
       <c r="P65">
-        <v>-5.1144273</v>
+        <v>-5.249894400000001</v>
       </c>
       <c r="Q65">
-        <v>-4.5044273</v>
+        <v>-4.6398944</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3016506234859909</v>
+        <v>0.3087575852494907</v>
       </c>
       <c r="T65">
-        <v>2.474271071236853</v>
+        <v>2.543000823215655</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1001824691857179</v>
+        <v>0.09861711810469109</v>
       </c>
       <c r="W65">
-        <v>0.2121769737660077</v>
+        <v>0.2125460835509138</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4007298767428717</v>
+        <v>0.3944684724187644</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2471822241624015</v>
+        <v>0.2490822241624015</v>
       </c>
       <c r="C66">
-        <v>-6.765515194826428</v>
+        <v>-7.85582845635961</v>
       </c>
       <c r="D66">
-        <v>34.69848480517357</v>
+        <v>34.37417154364039</v>
       </c>
       <c r="E66">
-        <v>38.424</v>
+        <v>39.19</v>
       </c>
       <c r="F66">
-        <v>49.024</v>
+        <v>49.79</v>
       </c>
       <c r="G66">
         <v>7.56</v>
@@ -6699,37 +6699,37 @@
         <v>4.56</v>
       </c>
       <c r="M66">
-        <v>11.5598592</v>
+        <v>11.740482</v>
       </c>
       <c r="N66">
-        <v>-6.9998592</v>
+        <v>-7.180482</v>
       </c>
       <c r="O66">
-        <v>-1.7499648</v>
+        <v>-1.7951205</v>
       </c>
       <c r="P66">
-        <v>-5.249894400000001</v>
+        <v>-5.3853615</v>
       </c>
       <c r="Q66">
-        <v>-4.6398944</v>
+        <v>-4.7753615</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3087575852494907</v>
+        <v>0.3162706591137618</v>
       </c>
       <c r="T66">
-        <v>2.543000823215655</v>
+        <v>2.615657989593245</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.09861711810469109</v>
+        <v>0.09709993167231123</v>
       </c>
       <c r="W66">
-        <v>0.2125460835509138</v>
+        <v>0.212903836111669</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3944684724187644</v>
+        <v>0.3883997266892449</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2490822241624015</v>
+        <v>0.2509822241624015</v>
       </c>
       <c r="C67">
-        <v>-7.85582845635961</v>
+        <v>-8.940135396444362</v>
       </c>
       <c r="D67">
-        <v>34.37417154364039</v>
+        <v>34.05586460355563</v>
       </c>
       <c r="E67">
-        <v>39.19</v>
+        <v>39.956</v>
       </c>
       <c r="F67">
-        <v>49.79</v>
+        <v>50.556</v>
       </c>
       <c r="G67">
         <v>7.56</v>
@@ -6781,37 +6781,37 @@
         <v>4.56</v>
       </c>
       <c r="M67">
-        <v>11.740482</v>
+        <v>11.9211048</v>
       </c>
       <c r="N67">
-        <v>-7.180482</v>
+        <v>-7.361104800000001</v>
       </c>
       <c r="O67">
-        <v>-1.7951205</v>
+        <v>-1.8402762</v>
       </c>
       <c r="P67">
-        <v>-5.3853615</v>
+        <v>-5.520828600000001</v>
       </c>
       <c r="Q67">
-        <v>-4.7753615</v>
+        <v>-4.9108286</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3162706591137618</v>
+        <v>0.3242256784994607</v>
       </c>
       <c r="T67">
-        <v>2.615657989593245</v>
+        <v>2.692589106934223</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.09709993167231123</v>
+        <v>0.09562872058636712</v>
       </c>
       <c r="W67">
-        <v>0.212903836111669</v>
+        <v>0.2132507476857347</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3883997266892449</v>
+        <v>0.3825148823454685</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2509822241624015</v>
+        <v>0.2528822241624015</v>
       </c>
       <c r="C68">
-        <v>-8.940135396444362</v>
+        <v>-10.01860134087043</v>
       </c>
       <c r="D68">
-        <v>34.05586460355563</v>
+        <v>33.74339865912957</v>
       </c>
       <c r="E68">
-        <v>39.956</v>
+        <v>40.722</v>
       </c>
       <c r="F68">
-        <v>50.556</v>
+        <v>51.322</v>
       </c>
       <c r="G68">
         <v>7.56</v>
@@ -6863,37 +6863,37 @@
         <v>4.56</v>
       </c>
       <c r="M68">
-        <v>11.9211048</v>
+        <v>12.1017276</v>
       </c>
       <c r="N68">
-        <v>-7.361104800000001</v>
+        <v>-7.541727600000001</v>
       </c>
       <c r="O68">
-        <v>-1.8402762</v>
+        <v>-1.8854319</v>
       </c>
       <c r="P68">
-        <v>-5.520828600000001</v>
+        <v>-5.6562957</v>
       </c>
       <c r="Q68">
-        <v>-4.9108286</v>
+        <v>-5.0462957</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3242256784994607</v>
+        <v>0.3326628202721716</v>
       </c>
       <c r="T68">
-        <v>2.692589106934223</v>
+        <v>2.77418271623526</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.09562872058636712</v>
+        <v>0.09420142624925716</v>
       </c>
       <c r="W68">
-        <v>0.2132507476857347</v>
+        <v>0.2135873036904252</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3825148823454685</v>
+        <v>0.3768057049970287</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2528822241624015</v>
+        <v>0.2547822241624015</v>
       </c>
       <c r="C69">
-        <v>-10.01860134087043</v>
+        <v>-11.09138560306932</v>
       </c>
       <c r="D69">
-        <v>33.74339865912957</v>
+        <v>33.43661439693068</v>
       </c>
       <c r="E69">
-        <v>40.722</v>
+        <v>41.488</v>
       </c>
       <c r="F69">
-        <v>51.322</v>
+        <v>52.088</v>
       </c>
       <c r="G69">
         <v>7.56</v>
@@ -6945,37 +6945,37 @@
         <v>4.56</v>
       </c>
       <c r="M69">
-        <v>12.1017276</v>
+        <v>12.2823504</v>
       </c>
       <c r="N69">
-        <v>-7.541727600000001</v>
+        <v>-7.722350400000001</v>
       </c>
       <c r="O69">
-        <v>-1.8854319</v>
+        <v>-1.9305876</v>
       </c>
       <c r="P69">
-        <v>-5.6562957</v>
+        <v>-5.791762800000001</v>
       </c>
       <c r="Q69">
-        <v>-5.0462957</v>
+        <v>-5.1817628</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3326628202721716</v>
+        <v>0.3416272834056771</v>
       </c>
       <c r="T69">
-        <v>2.77418271623526</v>
+        <v>2.860875926117612</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.09420142624925716</v>
+        <v>0.09281611115735632</v>
       </c>
       <c r="W69">
-        <v>0.2135873036904252</v>
+        <v>0.2139139609890954</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3768057049970287</v>
+        <v>0.3712644446294253</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2547822241624015</v>
+        <v>0.2566822241624015</v>
       </c>
       <c r="C70">
-        <v>-11.09138560306932</v>
+        <v>-12.15864175496406</v>
       </c>
       <c r="D70">
-        <v>33.43661439693068</v>
+        <v>33.13535824503594</v>
       </c>
       <c r="E70">
-        <v>41.488</v>
+        <v>42.254</v>
       </c>
       <c r="F70">
-        <v>52.088</v>
+        <v>52.854</v>
       </c>
       <c r="G70">
         <v>7.56</v>
@@ -7027,37 +7027,37 @@
         <v>4.56</v>
       </c>
       <c r="M70">
-        <v>12.2823504</v>
+        <v>12.4629732</v>
       </c>
       <c r="N70">
-        <v>-7.722350400000001</v>
+        <v>-7.902973200000001</v>
       </c>
       <c r="O70">
-        <v>-1.9305876</v>
+        <v>-1.9757433</v>
       </c>
       <c r="P70">
-        <v>-5.791762800000001</v>
+        <v>-5.9272299</v>
       </c>
       <c r="Q70">
-        <v>-5.1817628</v>
+        <v>-5.3172299</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3416272834056771</v>
+        <v>0.3511700989994086</v>
       </c>
       <c r="T70">
-        <v>2.860875926117612</v>
+        <v>2.953162246314954</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.09281611115735632</v>
+        <v>0.09147095012609029</v>
       </c>
       <c r="W70">
-        <v>0.2139139609890954</v>
+        <v>0.2142311499602679</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3712644446294253</v>
+        <v>0.3658838005043612</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2566822241624015</v>
+        <v>0.2585822241624015</v>
       </c>
       <c r="C71">
-        <v>-12.15864175496406</v>
+        <v>-13.22051788330793</v>
       </c>
       <c r="D71">
-        <v>33.13535824503594</v>
+        <v>32.83948211669207</v>
       </c>
       <c r="E71">
-        <v>42.254</v>
+        <v>43.02</v>
       </c>
       <c r="F71">
-        <v>52.854</v>
+        <v>53.62</v>
       </c>
       <c r="G71">
         <v>7.56</v>
@@ -7109,37 +7109,37 @@
         <v>4.56</v>
       </c>
       <c r="M71">
-        <v>12.4629732</v>
+        <v>12.643596</v>
       </c>
       <c r="N71">
-        <v>-7.902973200000001</v>
+        <v>-8.083596000000004</v>
       </c>
       <c r="O71">
-        <v>-1.9757433</v>
+        <v>-2.020899000000001</v>
       </c>
       <c r="P71">
-        <v>-5.9272299</v>
+        <v>-6.062697000000003</v>
       </c>
       <c r="Q71">
-        <v>-5.3172299</v>
+        <v>-5.452697000000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3511700989994086</v>
+        <v>0.3613491022993888</v>
       </c>
       <c r="T71">
-        <v>2.953162246314954</v>
+        <v>3.051600987858786</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.09147095012609029</v>
+        <v>0.09016422226714613</v>
       </c>
       <c r="W71">
-        <v>0.2142311499602679</v>
+        <v>0.214539276389407</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3658838005043612</v>
+        <v>0.3606568890685844</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2585822241624015</v>
+        <v>0.2604822241624015</v>
       </c>
       <c r="C72">
-        <v>-13.22051788330793</v>
+        <v>-14.27715683241121</v>
       </c>
       <c r="D72">
-        <v>32.83948211669207</v>
+        <v>32.54884316758879</v>
       </c>
       <c r="E72">
-        <v>43.02</v>
+        <v>43.786</v>
       </c>
       <c r="F72">
-        <v>53.62</v>
+        <v>54.386</v>
       </c>
       <c r="G72">
         <v>7.56</v>
@@ -7191,37 +7191,37 @@
         <v>4.56</v>
       </c>
       <c r="M72">
-        <v>12.643596</v>
+        <v>12.8242188</v>
       </c>
       <c r="N72">
-        <v>-8.083596000000004</v>
+        <v>-8.264218800000002</v>
       </c>
       <c r="O72">
-        <v>-2.020899000000001</v>
+        <v>-2.0660547</v>
       </c>
       <c r="P72">
-        <v>-6.062697000000003</v>
+        <v>-6.198164100000001</v>
       </c>
       <c r="Q72">
-        <v>-5.452697000000002</v>
+        <v>-5.588164100000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3613491022993888</v>
+        <v>0.372230105826954</v>
       </c>
       <c r="T72">
-        <v>3.051600987858786</v>
+        <v>3.156828608129779</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.09016422226714613</v>
+        <v>0.08889430364366521</v>
       </c>
       <c r="W72">
-        <v>0.214539276389407</v>
+        <v>0.2148387232008238</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3606568890685844</v>
+        <v>0.3555772145746607</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2604822241624015</v>
+        <v>0.2623822241624015</v>
       </c>
       <c r="C73">
-        <v>-14.2771568324112</v>
+        <v>-15.32869643409174</v>
       </c>
       <c r="D73">
-        <v>32.54884316758879</v>
+        <v>32.26330356590825</v>
       </c>
       <c r="E73">
-        <v>43.78599999999999</v>
+        <v>44.55199999999999</v>
       </c>
       <c r="F73">
-        <v>54.386</v>
+        <v>55.15199999999999</v>
       </c>
       <c r="G73">
         <v>7.56</v>
@@ -7273,37 +7273,37 @@
         <v>4.56</v>
       </c>
       <c r="M73">
-        <v>12.8242188</v>
+        <v>13.0048416</v>
       </c>
       <c r="N73">
-        <v>-8.264218799999998</v>
+        <v>-8.4448416</v>
       </c>
       <c r="O73">
-        <v>-2.0660547</v>
+        <v>-2.1112104</v>
       </c>
       <c r="P73">
-        <v>-6.198164099999999</v>
+        <v>-6.3336312</v>
       </c>
       <c r="Q73">
-        <v>-5.588164099999998</v>
+        <v>-5.7236312</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3722301058269539</v>
+        <v>0.3838883238922022</v>
       </c>
       <c r="T73">
-        <v>3.156828608129778</v>
+        <v>3.269572486991556</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08889430364366523</v>
+        <v>0.0876596605375032</v>
       </c>
       <c r="W73">
-        <v>0.2148387232008238</v>
+        <v>0.2151298520452568</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.355577214574661</v>
+        <v>0.3506386421500127</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2623822241624015</v>
+        <v>0.2642822241624014</v>
       </c>
       <c r="C74">
-        <v>-15.32869643409174</v>
+        <v>-16.37526972562716</v>
       </c>
       <c r="D74">
-        <v>32.26330356590825</v>
+        <v>31.98273027437283</v>
       </c>
       <c r="E74">
-        <v>44.55199999999999</v>
+        <v>45.31799999999999</v>
       </c>
       <c r="F74">
-        <v>55.15199999999999</v>
+        <v>55.91799999999999</v>
       </c>
       <c r="G74">
         <v>7.56</v>
@@ -7355,37 +7355,37 @@
         <v>4.56</v>
       </c>
       <c r="M74">
-        <v>13.0048416</v>
+        <v>13.1854644</v>
       </c>
       <c r="N74">
-        <v>-8.4448416</v>
+        <v>-8.625464399999998</v>
       </c>
       <c r="O74">
-        <v>-2.1112104</v>
+        <v>-2.1563661</v>
       </c>
       <c r="P74">
-        <v>-6.3336312</v>
+        <v>-6.469098299999999</v>
       </c>
       <c r="Q74">
-        <v>-5.7236312</v>
+        <v>-5.859098299999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3838883238922022</v>
+        <v>0.3964101136659874</v>
       </c>
       <c r="T74">
-        <v>3.269572486991556</v>
+        <v>3.390667764287539</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0876596605375032</v>
+        <v>0.08645884326986616</v>
       </c>
       <c r="W74">
-        <v>0.2151298520452568</v>
+        <v>0.2154130047569656</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3506386421500127</v>
+        <v>0.3458353730794648</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2642822241624014</v>
+        <v>0.2661822241624014</v>
       </c>
       <c r="C75">
-        <v>-16.37526972562716</v>
+        <v>-17.41700515643274</v>
       </c>
       <c r="D75">
-        <v>31.98273027437283</v>
+        <v>31.70699484356726</v>
       </c>
       <c r="E75">
-        <v>45.31799999999999</v>
+        <v>46.084</v>
       </c>
       <c r="F75">
-        <v>55.91799999999999</v>
+        <v>56.684</v>
       </c>
       <c r="G75">
         <v>7.56</v>
@@ -7437,37 +7437,37 @@
         <v>4.56</v>
       </c>
       <c r="M75">
-        <v>13.1854644</v>
+        <v>13.3660872</v>
       </c>
       <c r="N75">
-        <v>-8.625464399999998</v>
+        <v>-8.8060872</v>
       </c>
       <c r="O75">
-        <v>-2.1563661</v>
+        <v>-2.2015218</v>
       </c>
       <c r="P75">
-        <v>-6.469098299999999</v>
+        <v>-6.6045654</v>
       </c>
       <c r="Q75">
-        <v>-5.859098299999999</v>
+        <v>-5.9945654</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3964101136659874</v>
+        <v>0.4098951180377562</v>
       </c>
       <c r="T75">
-        <v>3.390667764287539</v>
+        <v>3.521078062913983</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08645884326986616</v>
+        <v>0.08529048052297608</v>
       </c>
       <c r="W75">
-        <v>0.2154130047569656</v>
+        <v>0.2156885046926822</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3458353730794648</v>
+        <v>0.3411619220919043</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2661822241624014</v>
+        <v>0.2680822241624015</v>
       </c>
       <c r="C76">
-        <v>-17.41700515643274</v>
+        <v>-18.45402678413952</v>
       </c>
       <c r="D76">
-        <v>31.70699484356726</v>
+        <v>31.43597321586047</v>
       </c>
       <c r="E76">
-        <v>46.084</v>
+        <v>46.84999999999999</v>
       </c>
       <c r="F76">
-        <v>56.684</v>
+        <v>57.45</v>
       </c>
       <c r="G76">
         <v>7.56</v>
@@ -7519,37 +7519,37 @@
         <v>4.56</v>
       </c>
       <c r="M76">
-        <v>13.3660872</v>
+        <v>13.54671</v>
       </c>
       <c r="N76">
-        <v>-8.8060872</v>
+        <v>-8.986709999999999</v>
       </c>
       <c r="O76">
-        <v>-2.2015218</v>
+        <v>-2.2466775</v>
       </c>
       <c r="P76">
-        <v>-6.6045654</v>
+        <v>-6.740032499999999</v>
       </c>
       <c r="Q76">
-        <v>-5.9945654</v>
+        <v>-6.130032499999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4098951180377562</v>
+        <v>0.4244589227592665</v>
       </c>
       <c r="T76">
-        <v>3.521078062913983</v>
+        <v>3.661921185430542</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08529048052297608</v>
+        <v>0.08415327411600307</v>
       </c>
       <c r="W76">
-        <v>0.2156885046926822</v>
+        <v>0.2159566579634465</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3411619220919043</v>
+        <v>0.3366130964640124</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2680822241624015</v>
+        <v>0.2699822241624015</v>
       </c>
       <c r="C77">
-        <v>-18.45402678413952</v>
+        <v>-19.48645446070172</v>
       </c>
       <c r="D77">
-        <v>31.43597321586047</v>
+        <v>31.16954553929827</v>
       </c>
       <c r="E77">
-        <v>46.84999999999999</v>
+        <v>47.61599999999999</v>
       </c>
       <c r="F77">
-        <v>57.45</v>
+        <v>58.21599999999999</v>
       </c>
       <c r="G77">
         <v>7.56</v>
@@ -7601,37 +7601,37 @@
         <v>4.56</v>
       </c>
       <c r="M77">
-        <v>13.54671</v>
+        <v>13.7273328</v>
       </c>
       <c r="N77">
-        <v>-8.986709999999999</v>
+        <v>-9.167332800000001</v>
       </c>
       <c r="O77">
-        <v>-2.2466775</v>
+        <v>-2.2918332</v>
       </c>
       <c r="P77">
-        <v>-6.740032499999999</v>
+        <v>-6.8754996</v>
       </c>
       <c r="Q77">
-        <v>-6.130032499999999</v>
+        <v>-6.2654996</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4244589227592665</v>
+        <v>0.440236377874236</v>
       </c>
       <c r="T77">
-        <v>3.661921185430542</v>
+        <v>3.814501234823482</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08415327411600307</v>
+        <v>0.08304599419342408</v>
       </c>
       <c r="W77">
-        <v>0.2159566579634465</v>
+        <v>0.2162177545691906</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3366130964640124</v>
+        <v>0.3321839767736963</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2699822241624015</v>
+        <v>0.2718822241624015</v>
       </c>
       <c r="C78">
-        <v>-19.48645446070172</v>
+        <v>-20.51440400911967</v>
       </c>
       <c r="D78">
-        <v>31.16954553929827</v>
+        <v>30.90759599088033</v>
       </c>
       <c r="E78">
-        <v>47.61599999999999</v>
+        <v>48.382</v>
       </c>
       <c r="F78">
-        <v>58.21599999999999</v>
+        <v>58.982</v>
       </c>
       <c r="G78">
         <v>7.56</v>
@@ -7683,37 +7683,37 @@
         <v>4.56</v>
       </c>
       <c r="M78">
-        <v>13.7273328</v>
+        <v>13.9079556</v>
       </c>
       <c r="N78">
-        <v>-9.167332800000001</v>
+        <v>-9.347955600000002</v>
       </c>
       <c r="O78">
-        <v>-2.2918332</v>
+        <v>-2.336988900000001</v>
       </c>
       <c r="P78">
-        <v>-6.8754996</v>
+        <v>-7.010966700000002</v>
       </c>
       <c r="Q78">
-        <v>-6.2654996</v>
+        <v>-6.400966700000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.440236377874236</v>
+        <v>0.4573857856078984</v>
       </c>
       <c r="T78">
-        <v>3.814501234823482</v>
+        <v>3.980349114598416</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08304599419342408</v>
+        <v>0.08196747478831466</v>
       </c>
       <c r="W78">
-        <v>0.2162177545691906</v>
+        <v>0.2164720694449154</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3321839767736963</v>
+        <v>0.3278698991532586</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2718822241624015</v>
+        <v>0.2737822241624015</v>
       </c>
       <c r="C79">
-        <v>-20.51440400911967</v>
+        <v>-21.537987391326</v>
       </c>
       <c r="D79">
-        <v>30.90759599088033</v>
+        <v>30.650012608674</v>
       </c>
       <c r="E79">
-        <v>48.382</v>
+        <v>49.148</v>
       </c>
       <c r="F79">
-        <v>58.982</v>
+        <v>59.748</v>
       </c>
       <c r="G79">
         <v>7.56</v>
@@ -7765,37 +7765,37 @@
         <v>4.56</v>
       </c>
       <c r="M79">
-        <v>13.9079556</v>
+        <v>14.0885784</v>
       </c>
       <c r="N79">
-        <v>-9.347955600000002</v>
+        <v>-9.528578400000001</v>
       </c>
       <c r="O79">
-        <v>-2.336988900000001</v>
+        <v>-2.3821446</v>
       </c>
       <c r="P79">
-        <v>-7.010966700000002</v>
+        <v>-7.146433800000001</v>
       </c>
       <c r="Q79">
-        <v>-6.400966700000001</v>
+        <v>-6.5364338</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4573857856078984</v>
+        <v>0.4760942304082574</v>
       </c>
       <c r="T79">
-        <v>3.980349114598416</v>
+        <v>4.161274074352889</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08196747478831466</v>
+        <v>0.08091660972692603</v>
       </c>
       <c r="W79">
-        <v>0.2164720694449154</v>
+        <v>0.2167198634263909</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3278698991532586</v>
+        <v>0.3236664389077041</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2737822241624015</v>
+        <v>0.2756822241624015</v>
       </c>
       <c r="C80">
-        <v>-21.537987391326</v>
+        <v>-22.55731286774622</v>
       </c>
       <c r="D80">
-        <v>30.650012608674</v>
+        <v>30.39668713225378</v>
       </c>
       <c r="E80">
-        <v>49.148</v>
+        <v>49.91399999999999</v>
       </c>
       <c r="F80">
-        <v>59.748</v>
+        <v>60.514</v>
       </c>
       <c r="G80">
         <v>7.56</v>
@@ -7847,37 +7847,37 @@
         <v>4.56</v>
       </c>
       <c r="M80">
-        <v>14.0885784</v>
+        <v>14.2692012</v>
       </c>
       <c r="N80">
-        <v>-9.528578400000001</v>
+        <v>-9.709201199999999</v>
       </c>
       <c r="O80">
-        <v>-2.3821446</v>
+        <v>-2.4273003</v>
       </c>
       <c r="P80">
-        <v>-7.146433800000001</v>
+        <v>-7.281900899999999</v>
       </c>
       <c r="Q80">
-        <v>-6.5364338</v>
+        <v>-6.671900899999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4760942304082574</v>
+        <v>0.4965844318562697</v>
       </c>
       <c r="T80">
-        <v>4.161274074352889</v>
+        <v>4.359429982655408</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08091660972692603</v>
+        <v>0.07989234884430671</v>
       </c>
       <c r="W80">
-        <v>0.2167198634263909</v>
+        <v>0.2169613841425125</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3236664389077041</v>
+        <v>0.319569395377227</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2756822241624015</v>
+        <v>0.2775822241624015</v>
       </c>
       <c r="C81">
-        <v>-22.55731286774622</v>
+        <v>-23.57248514901148</v>
       </c>
       <c r="D81">
-        <v>30.39668713225378</v>
+        <v>30.14751485098851</v>
       </c>
       <c r="E81">
-        <v>49.91399999999999</v>
+        <v>50.68</v>
       </c>
       <c r="F81">
-        <v>60.514</v>
+        <v>61.28</v>
       </c>
       <c r="G81">
         <v>7.56</v>
@@ -7929,37 +7929,37 @@
         <v>4.56</v>
       </c>
       <c r="M81">
-        <v>14.2692012</v>
+        <v>14.449824</v>
       </c>
       <c r="N81">
-        <v>-9.709201199999999</v>
+        <v>-9.889824000000001</v>
       </c>
       <c r="O81">
-        <v>-2.4273003</v>
+        <v>-2.472456</v>
       </c>
       <c r="P81">
-        <v>-7.281900899999999</v>
+        <v>-7.417368000000001</v>
       </c>
       <c r="Q81">
-        <v>-6.671900899999999</v>
+        <v>-6.807368</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4965844318562697</v>
+        <v>0.5191236534490832</v>
       </c>
       <c r="T81">
-        <v>4.359429982655408</v>
+        <v>4.577401481788179</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07989234884430671</v>
+        <v>0.07889369448375287</v>
       </c>
       <c r="W81">
-        <v>0.2169613841425125</v>
+        <v>0.2171968668407311</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.319569395377227</v>
+        <v>0.3155747779350115</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2775822241624015</v>
+        <v>0.2794822241624015</v>
       </c>
       <c r="C82">
-        <v>-23.57248514901148</v>
+        <v>-24.58360554027013</v>
       </c>
       <c r="D82">
-        <v>30.14751485098851</v>
+        <v>29.90239445972987</v>
       </c>
       <c r="E82">
-        <v>50.68</v>
+        <v>51.446</v>
       </c>
       <c r="F82">
-        <v>61.28</v>
+        <v>62.046</v>
       </c>
       <c r="G82">
         <v>7.56</v>
@@ -8011,37 +8011,37 @@
         <v>4.56</v>
       </c>
       <c r="M82">
-        <v>14.449824</v>
+        <v>14.6304468</v>
       </c>
       <c r="N82">
-        <v>-9.889824000000001</v>
+        <v>-10.0704468</v>
       </c>
       <c r="O82">
-        <v>-2.472456</v>
+        <v>-2.5176117</v>
       </c>
       <c r="P82">
-        <v>-7.417368000000001</v>
+        <v>-7.552835099999999</v>
       </c>
       <c r="Q82">
-        <v>-6.807368</v>
+        <v>-6.942835099999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5191236534490832</v>
+        <v>0.5440354246832455</v>
       </c>
       <c r="T82">
-        <v>4.577401481788179</v>
+        <v>4.818317349250715</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07889369448375287</v>
+        <v>0.0779196982555584</v>
       </c>
       <c r="W82">
-        <v>0.2171968668407311</v>
+        <v>0.2174265351513393</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3155747779350115</v>
+        <v>0.3116787930222337</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2794822241624015</v>
+        <v>0.2813822241624015</v>
       </c>
       <c r="C83">
-        <v>-24.58360554027013</v>
+        <v>-25.5907720785159</v>
       </c>
       <c r="D83">
-        <v>29.90239445972987</v>
+        <v>29.66122792148409</v>
       </c>
       <c r="E83">
-        <v>51.446</v>
+        <v>52.212</v>
       </c>
       <c r="F83">
-        <v>62.046</v>
+        <v>62.812</v>
       </c>
       <c r="G83">
         <v>7.56</v>
@@ -8093,37 +8093,37 @@
         <v>4.56</v>
       </c>
       <c r="M83">
-        <v>14.6304468</v>
+        <v>14.8110696</v>
       </c>
       <c r="N83">
-        <v>-10.0704468</v>
+        <v>-10.2510696</v>
       </c>
       <c r="O83">
-        <v>-2.5176117</v>
+        <v>-2.5627674</v>
       </c>
       <c r="P83">
-        <v>-7.552835099999999</v>
+        <v>-7.688302200000001</v>
       </c>
       <c r="Q83">
-        <v>-6.942835099999999</v>
+        <v>-7.0783022</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5440354246832455</v>
+        <v>0.5717151704989814</v>
       </c>
       <c r="T83">
-        <v>4.818317349250715</v>
+        <v>5.086001646431311</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.0779196982555584</v>
+        <v>0.07696945803292964</v>
       </c>
       <c r="W83">
-        <v>0.2174265351513393</v>
+        <v>0.2176506017958352</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3116787930222337</v>
+        <v>0.3078778321317185</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2813822241624015</v>
+        <v>0.2832822241624015</v>
       </c>
       <c r="C84">
-        <v>-25.5907720785159</v>
+        <v>-26.59407966332394</v>
       </c>
       <c r="D84">
-        <v>29.66122792148409</v>
+        <v>29.42392033667606</v>
       </c>
       <c r="E84">
-        <v>52.212</v>
+        <v>52.978</v>
       </c>
       <c r="F84">
-        <v>62.812</v>
+        <v>63.578</v>
       </c>
       <c r="G84">
         <v>7.56</v>
@@ -8175,37 +8175,37 @@
         <v>4.56</v>
       </c>
       <c r="M84">
-        <v>14.8110696</v>
+        <v>14.9916924</v>
       </c>
       <c r="N84">
-        <v>-10.2510696</v>
+        <v>-10.4316924</v>
       </c>
       <c r="O84">
-        <v>-2.5627674</v>
+        <v>-2.607923100000001</v>
       </c>
       <c r="P84">
-        <v>-7.688302200000001</v>
+        <v>-7.823769300000002</v>
       </c>
       <c r="Q84">
-        <v>-7.0783022</v>
+        <v>-7.213769300000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5717151704989814</v>
+        <v>0.6026513569989215</v>
       </c>
       <c r="T84">
-        <v>5.086001646431311</v>
+        <v>5.385178213868446</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07696945803292964</v>
+        <v>0.076042115165063</v>
       </c>
       <c r="W84">
-        <v>0.2176506017958352</v>
+        <v>0.2178692692440782</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3078778321317185</v>
+        <v>0.3041684606602519</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2832822241624015</v>
+        <v>0.2851822241624015</v>
       </c>
       <c r="C85">
-        <v>-26.59407966332394</v>
+        <v>-27.59362018136073</v>
       </c>
       <c r="D85">
-        <v>29.42392033667606</v>
+        <v>29.19037981863928</v>
       </c>
       <c r="E85">
-        <v>52.978</v>
+        <v>53.74400000000001</v>
       </c>
       <c r="F85">
-        <v>63.578</v>
+        <v>64.34400000000001</v>
       </c>
       <c r="G85">
         <v>7.56</v>
@@ -8257,37 +8257,37 @@
         <v>4.56</v>
       </c>
       <c r="M85">
-        <v>14.9916924</v>
+        <v>15.1723152</v>
       </c>
       <c r="N85">
-        <v>-10.4316924</v>
+        <v>-10.6123152</v>
       </c>
       <c r="O85">
-        <v>-2.607923100000001</v>
+        <v>-2.653078800000001</v>
       </c>
       <c r="P85">
-        <v>-7.823769300000002</v>
+        <v>-7.959236400000004</v>
       </c>
       <c r="Q85">
-        <v>-7.213769300000002</v>
+        <v>-7.349236400000003</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6026513569989215</v>
+        <v>0.6374545668113543</v>
       </c>
       <c r="T85">
-        <v>5.385178213868446</v>
+        <v>5.721751852235227</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.076042115165063</v>
+        <v>0.07513685188928844</v>
       </c>
       <c r="W85">
-        <v>0.2178692692440782</v>
+        <v>0.2180827303245058</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3041684606602519</v>
+        <v>0.3005474075571537</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2851822241624015</v>
+        <v>0.2870822241624015</v>
       </c>
       <c r="C86">
-        <v>-27.59362018136072</v>
+        <v>-28.58948262501129</v>
       </c>
       <c r="D86">
-        <v>29.19037981863928</v>
+        <v>28.96051737498871</v>
       </c>
       <c r="E86">
-        <v>53.74399999999999</v>
+        <v>54.51</v>
       </c>
       <c r="F86">
-        <v>64.34399999999999</v>
+        <v>65.11</v>
       </c>
       <c r="G86">
         <v>7.56</v>
@@ -8339,37 +8339,37 @@
         <v>4.56</v>
       </c>
       <c r="M86">
-        <v>15.1723152</v>
+        <v>15.352938</v>
       </c>
       <c r="N86">
-        <v>-10.6123152</v>
+        <v>-10.792938</v>
       </c>
       <c r="O86">
-        <v>-2.6530788</v>
+        <v>-2.6982345</v>
       </c>
       <c r="P86">
-        <v>-7.959236400000001</v>
+        <v>-8.0947035</v>
       </c>
       <c r="Q86">
-        <v>-7.349236400000001</v>
+        <v>-7.484703499999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6374545668113538</v>
+        <v>0.6768982045987774</v>
       </c>
       <c r="T86">
-        <v>5.721751852235222</v>
+        <v>6.10320197571757</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07513685188928845</v>
+        <v>0.07425288892588505</v>
       </c>
       <c r="W86">
-        <v>0.2180827303245058</v>
+        <v>0.2182911687912763</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3005474075571537</v>
+        <v>0.2970115557035403</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2870822241624015</v>
+        <v>0.2889822241624015</v>
       </c>
       <c r="C87">
-        <v>-28.58948262501129</v>
+        <v>-29.58175320544537</v>
       </c>
       <c r="D87">
-        <v>28.96051737498871</v>
+        <v>28.73424679455461</v>
       </c>
       <c r="E87">
-        <v>54.51</v>
+        <v>55.27599999999999</v>
       </c>
       <c r="F87">
-        <v>65.11</v>
+        <v>65.87599999999999</v>
       </c>
       <c r="G87">
         <v>7.56</v>
@@ -8421,37 +8421,37 @@
         <v>4.56</v>
       </c>
       <c r="M87">
-        <v>15.352938</v>
+        <v>15.5335608</v>
       </c>
       <c r="N87">
-        <v>-10.792938</v>
+        <v>-10.9735608</v>
       </c>
       <c r="O87">
-        <v>-2.6982345</v>
+        <v>-2.743390199999999</v>
       </c>
       <c r="P87">
-        <v>-8.0947035</v>
+        <v>-8.230170599999997</v>
       </c>
       <c r="Q87">
-        <v>-7.484703499999999</v>
+        <v>-7.620170599999997</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6768982045987774</v>
+        <v>0.7219766477844043</v>
       </c>
       <c r="T87">
-        <v>6.10320197571757</v>
+        <v>6.53914497398311</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07425288892588505</v>
+        <v>0.07338948324070035</v>
       </c>
       <c r="W87">
-        <v>0.2182911687912763</v>
+        <v>0.2184947598518429</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2970115557035403</v>
+        <v>0.2935579329628015</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2889822241624015</v>
+        <v>0.2908822241624015</v>
       </c>
       <c r="C88">
-        <v>-29.58175320544537</v>
+        <v>-30.57051546042425</v>
       </c>
       <c r="D88">
-        <v>28.73424679455461</v>
+        <v>28.51148453957575</v>
       </c>
       <c r="E88">
-        <v>55.27599999999999</v>
+        <v>56.04199999999999</v>
       </c>
       <c r="F88">
-        <v>65.87599999999999</v>
+        <v>66.642</v>
       </c>
       <c r="G88">
         <v>7.56</v>
@@ -8503,37 +8503,37 @@
         <v>4.56</v>
       </c>
       <c r="M88">
-        <v>15.5335608</v>
+        <v>15.7141836</v>
       </c>
       <c r="N88">
-        <v>-10.9735608</v>
+        <v>-11.1541836</v>
       </c>
       <c r="O88">
-        <v>-2.743390199999999</v>
+        <v>-2.7885459</v>
       </c>
       <c r="P88">
-        <v>-8.230170599999997</v>
+        <v>-8.365637700000001</v>
       </c>
       <c r="Q88">
-        <v>-7.620170599999997</v>
+        <v>-7.7556377</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7219766477844043</v>
+        <v>0.7739902360755123</v>
       </c>
       <c r="T88">
-        <v>6.53914497398311</v>
+        <v>7.042156125827965</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07338948324070035</v>
+        <v>0.07254592596207161</v>
       </c>
       <c r="W88">
-        <v>0.2184947598518429</v>
+        <v>0.2186936706581435</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2935579329628015</v>
+        <v>0.2901837038482865</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2908822241624015</v>
+        <v>0.2927822241624015</v>
       </c>
       <c r="C89">
-        <v>-30.57051546042425</v>
+        <v>-31.55585035713154</v>
       </c>
       <c r="D89">
-        <v>28.51148453957575</v>
+        <v>28.29214964286846</v>
       </c>
       <c r="E89">
-        <v>56.04199999999999</v>
+        <v>56.808</v>
       </c>
       <c r="F89">
-        <v>66.642</v>
+        <v>67.408</v>
       </c>
       <c r="G89">
         <v>7.56</v>
@@ -8585,37 +8585,37 @@
         <v>4.56</v>
       </c>
       <c r="M89">
-        <v>15.7141836</v>
+        <v>15.8948064</v>
       </c>
       <c r="N89">
-        <v>-11.1541836</v>
+        <v>-11.3348064</v>
       </c>
       <c r="O89">
-        <v>-2.7885459</v>
+        <v>-2.8337016</v>
       </c>
       <c r="P89">
-        <v>-8.365637700000001</v>
+        <v>-8.5011048</v>
       </c>
       <c r="Q89">
-        <v>-7.7556377</v>
+        <v>-7.8911048</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7739902360755123</v>
+        <v>0.834672755748472</v>
       </c>
       <c r="T89">
-        <v>7.042156125827965</v>
+        <v>7.629002469646965</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07254592596207161</v>
+        <v>0.07172154043977534</v>
       </c>
       <c r="W89">
-        <v>0.2186936706581435</v>
+        <v>0.218888060764301</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2901837038482865</v>
+        <v>0.2868861617591013</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2927822241624015</v>
+        <v>0.2946822241624015</v>
       </c>
       <c r="C90">
-        <v>-31.55585035713154</v>
+        <v>-32.53783639029383</v>
       </c>
       <c r="D90">
-        <v>28.29214964286846</v>
+        <v>28.07616360970616</v>
       </c>
       <c r="E90">
-        <v>56.808</v>
+        <v>57.57399999999999</v>
       </c>
       <c r="F90">
-        <v>67.408</v>
+        <v>68.17399999999999</v>
       </c>
       <c r="G90">
         <v>7.56</v>
@@ -8667,37 +8667,37 @@
         <v>4.56</v>
       </c>
       <c r="M90">
-        <v>15.8948064</v>
+        <v>16.0754292</v>
       </c>
       <c r="N90">
-        <v>-11.3348064</v>
+        <v>-11.5154292</v>
       </c>
       <c r="O90">
-        <v>-2.8337016</v>
+        <v>-2.8788573</v>
       </c>
       <c r="P90">
-        <v>-8.5011048</v>
+        <v>-8.6365719</v>
       </c>
       <c r="Q90">
-        <v>-7.8911048</v>
+        <v>-8.0265719</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.834672755748472</v>
+        <v>0.9063884608165147</v>
       </c>
       <c r="T90">
-        <v>7.629002469646965</v>
+        <v>8.322548148705778</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07172154043977534</v>
+        <v>0.07091568043483405</v>
       </c>
       <c r="W90">
-        <v>0.218888060764301</v>
+        <v>0.2190780825534661</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2868861617591013</v>
+        <v>0.2836627217393362</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2946822241624015</v>
+        <v>0.2965822241624015</v>
       </c>
       <c r="C91">
-        <v>-32.53783639029383</v>
+        <v>-33.51654967584113</v>
       </c>
       <c r="D91">
-        <v>28.07616360970616</v>
+        <v>27.86345032415887</v>
       </c>
       <c r="E91">
-        <v>57.57399999999999</v>
+        <v>58.34</v>
       </c>
       <c r="F91">
-        <v>68.17399999999999</v>
+        <v>68.94</v>
       </c>
       <c r="G91">
         <v>7.56</v>
@@ -8749,37 +8749,37 @@
         <v>4.56</v>
       </c>
       <c r="M91">
-        <v>16.0754292</v>
+        <v>16.256052</v>
       </c>
       <c r="N91">
-        <v>-11.5154292</v>
+        <v>-11.696052</v>
       </c>
       <c r="O91">
-        <v>-2.8788573</v>
+        <v>-2.924013</v>
       </c>
       <c r="P91">
-        <v>-8.6365719</v>
+        <v>-8.772039000000001</v>
       </c>
       <c r="Q91">
-        <v>-8.0265719</v>
+        <v>-8.162039</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9063884608165147</v>
+        <v>0.9924473068981664</v>
       </c>
       <c r="T91">
-        <v>8.322548148705778</v>
+        <v>9.154802963576358</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07091568043483405</v>
+        <v>0.07012772843000255</v>
       </c>
       <c r="W91">
-        <v>0.2190780825534661</v>
+        <v>0.2192638816362054</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2836627217393362</v>
+        <v>0.2805109137200101</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2965822241624015</v>
+        <v>0.2984822241624015</v>
       </c>
       <c r="C92">
-        <v>-33.51654967584113</v>
+        <v>-34.49206404034141</v>
       </c>
       <c r="D92">
-        <v>27.86345032415887</v>
+        <v>27.65393595965859</v>
       </c>
       <c r="E92">
-        <v>58.34</v>
+        <v>59.106</v>
       </c>
       <c r="F92">
-        <v>68.94</v>
+        <v>69.706</v>
       </c>
       <c r="G92">
         <v>7.56</v>
@@ -8831,37 +8831,37 @@
         <v>4.56</v>
       </c>
       <c r="M92">
-        <v>16.256052</v>
+        <v>16.4366748</v>
       </c>
       <c r="N92">
-        <v>-11.696052</v>
+        <v>-11.8766748</v>
       </c>
       <c r="O92">
-        <v>-2.924013</v>
+        <v>-2.969168700000001</v>
       </c>
       <c r="P92">
-        <v>-8.772039000000001</v>
+        <v>-8.907506100000003</v>
       </c>
       <c r="Q92">
-        <v>-8.162039</v>
+        <v>-8.297506100000003</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.9924473068981664</v>
+        <v>1.097630340997963</v>
       </c>
       <c r="T92">
-        <v>9.154802963576358</v>
+        <v>10.17200329286262</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07012772843000255</v>
+        <v>0.06935709405165087</v>
       </c>
       <c r="W92">
-        <v>0.2192638816362054</v>
+        <v>0.2194455972226207</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2805109137200101</v>
+        <v>0.2774283762066034</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2984822241624015</v>
+        <v>0.3003822241624016</v>
       </c>
       <c r="C93">
-        <v>-34.49206404034141</v>
+        <v>-35.46445110643065</v>
       </c>
       <c r="D93">
-        <v>27.65393595965859</v>
+        <v>27.44754889356934</v>
       </c>
       <c r="E93">
-        <v>59.106</v>
+        <v>59.87199999999999</v>
       </c>
       <c r="F93">
-        <v>69.706</v>
+        <v>70.47199999999999</v>
       </c>
       <c r="G93">
         <v>7.56</v>
@@ -8913,37 +8913,37 @@
         <v>4.56</v>
       </c>
       <c r="M93">
-        <v>16.4366748</v>
+        <v>16.6172976</v>
       </c>
       <c r="N93">
-        <v>-11.8766748</v>
+        <v>-12.0572976</v>
       </c>
       <c r="O93">
-        <v>-2.969168700000001</v>
+        <v>-3.0143244</v>
       </c>
       <c r="P93">
-        <v>-8.907506100000003</v>
+        <v>-9.042973200000002</v>
       </c>
       <c r="Q93">
-        <v>-8.297506100000003</v>
+        <v>-8.432973200000003</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.097630340997963</v>
+        <v>1.229109133622709</v>
       </c>
       <c r="T93">
-        <v>10.17200329286262</v>
+        <v>11.44350370447045</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06935709405165087</v>
+        <v>0.06860321259456771</v>
       </c>
       <c r="W93">
-        <v>0.2194455972226207</v>
+        <v>0.219623362470201</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2774283762066034</v>
+        <v>0.2744128503782708</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3003822241624016</v>
+        <v>0.3022822241624015</v>
       </c>
       <c r="C94">
-        <v>-35.46445110643065</v>
+        <v>-36.43378037444558</v>
       </c>
       <c r="D94">
-        <v>27.44754889356934</v>
+        <v>27.24421962555442</v>
       </c>
       <c r="E94">
-        <v>59.87199999999999</v>
+        <v>60.638</v>
       </c>
       <c r="F94">
-        <v>70.47199999999999</v>
+        <v>71.238</v>
       </c>
       <c r="G94">
         <v>7.56</v>
@@ -8995,37 +8995,37 @@
         <v>4.56</v>
       </c>
       <c r="M94">
-        <v>16.6172976</v>
+        <v>16.7979204</v>
       </c>
       <c r="N94">
-        <v>-12.0572976</v>
+        <v>-12.2379204</v>
       </c>
       <c r="O94">
-        <v>-3.0143244</v>
+        <v>-3.0594801</v>
       </c>
       <c r="P94">
-        <v>-9.042973200000002</v>
+        <v>-9.1784403</v>
       </c>
       <c r="Q94">
-        <v>-8.432973200000003</v>
+        <v>-8.568440299999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.229109133622709</v>
+        <v>1.39815329556881</v>
       </c>
       <c r="T94">
-        <v>11.44350370447045</v>
+        <v>13.07828994796623</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06860321259456771</v>
+        <v>0.06786554364193796</v>
       </c>
       <c r="W94">
-        <v>0.219623362470201</v>
+        <v>0.219797304809231</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2744128503782708</v>
+        <v>0.2714621745677518</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3022822241624015</v>
+        <v>0.3041822241624015</v>
       </c>
       <c r="C95">
-        <v>-36.43378037444558</v>
+        <v>-37.40011930045473</v>
       </c>
       <c r="D95">
-        <v>27.24421962555442</v>
+        <v>27.04388069954527</v>
       </c>
       <c r="E95">
-        <v>60.638</v>
+        <v>61.404</v>
       </c>
       <c r="F95">
-        <v>71.238</v>
+        <v>72.004</v>
       </c>
       <c r="G95">
         <v>7.56</v>
@@ -9077,37 +9077,37 @@
         <v>4.56</v>
       </c>
       <c r="M95">
-        <v>16.7979204</v>
+        <v>16.9785432</v>
       </c>
       <c r="N95">
-        <v>-12.2379204</v>
+        <v>-12.4185432</v>
       </c>
       <c r="O95">
-        <v>-3.0594801</v>
+        <v>-3.104635800000001</v>
       </c>
       <c r="P95">
-        <v>-9.1784403</v>
+        <v>-9.313907400000002</v>
       </c>
       <c r="Q95">
-        <v>-8.568440299999999</v>
+        <v>-8.703907400000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.39815329556881</v>
+        <v>1.623545511496945</v>
       </c>
       <c r="T95">
-        <v>13.07828994796623</v>
+        <v>15.25800493929394</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06786554364193796</v>
+        <v>0.0671435697734067</v>
       </c>
       <c r="W95">
-        <v>0.219797304809231</v>
+        <v>0.2199675462474307</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2714621745677518</v>
+        <v>0.2685742790936267</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3041822241624015</v>
+        <v>0.3060822241624015</v>
       </c>
       <c r="C96">
-        <v>-37.40011930045473</v>
+        <v>-38.36353337087191</v>
       </c>
       <c r="D96">
-        <v>27.04388069954527</v>
+        <v>26.84646662912808</v>
       </c>
       <c r="E96">
-        <v>61.404</v>
+        <v>62.16999999999999</v>
       </c>
       <c r="F96">
-        <v>72.004</v>
+        <v>72.77</v>
       </c>
       <c r="G96">
         <v>7.56</v>
@@ -9159,37 +9159,37 @@
         <v>4.56</v>
       </c>
       <c r="M96">
-        <v>16.9785432</v>
+        <v>17.159166</v>
       </c>
       <c r="N96">
-        <v>-12.4185432</v>
+        <v>-12.599166</v>
       </c>
       <c r="O96">
-        <v>-3.104635800000001</v>
+        <v>-3.1497915</v>
       </c>
       <c r="P96">
-        <v>-9.313907400000002</v>
+        <v>-9.449374500000001</v>
       </c>
       <c r="Q96">
-        <v>-8.703907400000002</v>
+        <v>-8.839374500000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.623545511496945</v>
+        <v>1.939094613796335</v>
       </c>
       <c r="T96">
-        <v>15.25800493929394</v>
+        <v>18.30960592715274</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0671435697734067</v>
+        <v>0.06643679535473927</v>
       </c>
       <c r="W96">
-        <v>0.2199675462474307</v>
+        <v>0.2201342036553525</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2685742790936267</v>
+        <v>0.265747181418957</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3060822241624015</v>
+        <v>0.3079822241624015</v>
       </c>
       <c r="C97">
-        <v>-38.36353337087191</v>
+        <v>-39.32408617382529</v>
       </c>
       <c r="D97">
-        <v>26.84646662912808</v>
+        <v>26.65191382617472</v>
       </c>
       <c r="E97">
-        <v>62.16999999999999</v>
+        <v>62.936</v>
       </c>
       <c r="F97">
-        <v>72.77</v>
+        <v>73.536</v>
       </c>
       <c r="G97">
         <v>7.56</v>
@@ -9241,37 +9241,37 @@
         <v>4.56</v>
       </c>
       <c r="M97">
-        <v>17.159166</v>
+        <v>17.3397888</v>
       </c>
       <c r="N97">
-        <v>-12.599166</v>
+        <v>-12.7797888</v>
       </c>
       <c r="O97">
-        <v>-3.1497915</v>
+        <v>-3.194947200000001</v>
       </c>
       <c r="P97">
-        <v>-9.449374500000001</v>
+        <v>-9.584841600000001</v>
       </c>
       <c r="Q97">
-        <v>-8.839374500000002</v>
+        <v>-8.974841600000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.939094613796335</v>
+        <v>2.41241826724542</v>
       </c>
       <c r="T97">
-        <v>18.30960592715274</v>
+        <v>22.88700740894093</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06643679535473927</v>
+        <v>0.06574474540312739</v>
       </c>
       <c r="W97">
-        <v>0.2201342036553525</v>
+        <v>0.2202973890339426</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.265747181418957</v>
+        <v>0.2629789816125095</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3079822241624015</v>
+        <v>0.3098822241624015</v>
       </c>
       <c r="C98">
-        <v>-39.32408617382527</v>
+        <v>-40.28183946744564</v>
       </c>
       <c r="D98">
-        <v>26.65191382617472</v>
+        <v>26.46016053255435</v>
       </c>
       <c r="E98">
-        <v>62.93599999999999</v>
+        <v>63.70199999999999</v>
       </c>
       <c r="F98">
-        <v>73.53599999999999</v>
+        <v>74.30199999999999</v>
       </c>
       <c r="G98">
         <v>7.56</v>
@@ -9323,37 +9323,37 @@
         <v>4.56</v>
       </c>
       <c r="M98">
-        <v>17.3397888</v>
+        <v>17.5204116</v>
       </c>
       <c r="N98">
-        <v>-12.7797888</v>
+        <v>-12.9604116</v>
       </c>
       <c r="O98">
-        <v>-3.1949472</v>
+        <v>-3.2401029</v>
       </c>
       <c r="P98">
-        <v>-9.584841599999999</v>
+        <v>-9.7203087</v>
       </c>
       <c r="Q98">
-        <v>-8.974841599999998</v>
+        <v>-9.110308700000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.412418267245414</v>
+        <v>3.201291022993885</v>
       </c>
       <c r="T98">
-        <v>22.88700740894087</v>
+        <v>30.51600987858783</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0657447454031274</v>
+        <v>0.06506696452268279</v>
       </c>
       <c r="W98">
-        <v>0.2202973890339426</v>
+        <v>0.2204572097655514</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2629789816125095</v>
+        <v>0.2602678580907311</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3098822241624015</v>
+        <v>0.3117822241624015</v>
       </c>
       <c r="C99">
-        <v>-40.28183946744564</v>
+        <v>-41.23685324522787</v>
       </c>
       <c r="D99">
-        <v>26.46016053255435</v>
+        <v>26.27114675477213</v>
       </c>
       <c r="E99">
-        <v>63.70199999999999</v>
+        <v>64.468</v>
       </c>
       <c r="F99">
-        <v>74.30199999999999</v>
+        <v>75.068</v>
       </c>
       <c r="G99">
         <v>7.56</v>
@@ -9405,37 +9405,37 @@
         <v>4.56</v>
       </c>
       <c r="M99">
-        <v>17.5204116</v>
+        <v>17.7010344</v>
       </c>
       <c r="N99">
-        <v>-12.9604116</v>
+        <v>-13.1410344</v>
       </c>
       <c r="O99">
-        <v>-3.2401029</v>
+        <v>-3.285258600000001</v>
       </c>
       <c r="P99">
-        <v>-9.7203087</v>
+        <v>-9.855775800000002</v>
       </c>
       <c r="Q99">
-        <v>-9.110308700000001</v>
+        <v>-9.245775800000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.201291022993885</v>
+        <v>4.779036534490828</v>
       </c>
       <c r="T99">
-        <v>30.51600987858783</v>
+        <v>45.77401481788175</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06506696452268279</v>
+        <v>0.06440301590510439</v>
       </c>
       <c r="W99">
-        <v>0.2204572097655514</v>
+        <v>0.2206137688495764</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2602678580907311</v>
+        <v>0.2576120636204174</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3117822241624015</v>
+        <v>0.3136822241624015</v>
       </c>
       <c r="C100">
-        <v>-41.23685324522787</v>
+        <v>-42.18918579861075</v>
       </c>
       <c r="D100">
-        <v>26.27114675477213</v>
+        <v>26.08481420138924</v>
       </c>
       <c r="E100">
-        <v>64.468</v>
+        <v>65.23399999999999</v>
       </c>
       <c r="F100">
-        <v>75.068</v>
+        <v>75.83399999999999</v>
       </c>
       <c r="G100">
         <v>7.56</v>
@@ -9487,37 +9487,37 @@
         <v>4.56</v>
       </c>
       <c r="M100">
-        <v>17.7010344</v>
+        <v>17.8816572</v>
       </c>
       <c r="N100">
-        <v>-13.1410344</v>
+        <v>-13.3216572</v>
       </c>
       <c r="O100">
-        <v>-3.285258600000001</v>
+        <v>-3.3304143</v>
       </c>
       <c r="P100">
-        <v>-9.855775800000002</v>
+        <v>-9.9912429</v>
       </c>
       <c r="Q100">
-        <v>-9.245775800000001</v>
+        <v>-9.3812429</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.779036534490828</v>
+        <v>9.512273068981655</v>
       </c>
       <c r="T100">
-        <v>45.77401481788175</v>
+        <v>91.54802963576348</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06440301590510439</v>
+        <v>0.06375248039091141</v>
       </c>
       <c r="W100">
-        <v>0.2206137688495764</v>
+        <v>0.2207671651238231</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2576120636204174</v>
+        <v>0.2550099215636457</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3136822241624015</v>
-      </c>
-      <c r="C101">
-        <v>-42.18918579861075</v>
-      </c>
-      <c r="D101">
-        <v>26.08481420138924</v>
-      </c>
-      <c r="E101">
-        <v>65.23399999999999</v>
-      </c>
-      <c r="F101">
-        <v>75.83399999999999</v>
-      </c>
-      <c r="G101">
-        <v>7.56</v>
-      </c>
-      <c r="H101">
-        <v>66</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.17</v>
-      </c>
-      <c r="K101">
-        <v>0.6100000000000003</v>
-      </c>
-      <c r="L101">
-        <v>4.56</v>
-      </c>
-      <c r="M101">
-        <v>17.8816572</v>
-      </c>
-      <c r="N101">
-        <v>-13.3216572</v>
-      </c>
-      <c r="O101">
-        <v>-3.3304143</v>
-      </c>
-      <c r="P101">
-        <v>-9.9912429</v>
-      </c>
-      <c r="Q101">
-        <v>-9.3812429</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.512273068981655</v>
-      </c>
-      <c r="T101">
-        <v>91.54802963576348</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06375248039091141</v>
-      </c>
-      <c r="W101">
-        <v>0.2207671651238231</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2550099215636457</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
